--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02374FAD-AB9F-474A-AD13-46FC014FD059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAEFBDD-24C4-441E-B9AF-D30F2BC5E730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3694,29 +3694,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4127,13 +4127,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4235,22 +4235,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4262,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4288,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4323,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,13 +4345,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4415,13 +4415,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4459,22 +4459,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4535,22 +4535,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4608,22 +4608,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4660,13 +4660,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4789,13 +4789,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4821,13 +4821,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,13 +4970,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4989,22 +4989,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5100,13 +5100,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5143,13 +5143,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5157,22 +5157,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5196,17 +5196,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5223,6 +5212,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAEFBDD-24C4-441E-B9AF-D30F2BC5E730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B374F95E-34D8-4162-A7EA-AD591285EB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3694,29 +3694,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4127,13 +4127,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4235,22 +4235,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4262,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4288,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4323,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,13 +4345,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4415,13 +4415,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4459,22 +4459,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4535,22 +4535,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4608,22 +4608,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4660,13 +4660,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4789,13 +4789,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4821,13 +4821,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,13 +4970,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4989,22 +4989,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5100,13 +5100,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5143,13 +5143,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5157,22 +5157,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5196,6 +5196,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5212,17 +5223,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B374F95E-34D8-4162-A7EA-AD591285EB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C32A89-AA3D-4690-BBA8-811BBAFBD32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1317,10 +1317,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1821,14 +1817,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2314,6 +2302,49 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Kraft Heinz Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>KHC</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2322,12 +2353,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Kraft Heinz Company</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNS_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -3001,7 +3031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3694,29 +3724,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4006,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4026,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4058,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4108,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4091,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4101,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4127,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4154,10 +4187,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4180,18 +4213,23 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4203,7 +4241,7 @@
         <v>19.745207945921621</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4211,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4226,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4235,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4370,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4403,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4415,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4459,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4504,7 +4542,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4513,7 +4551,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4522,7 +4560,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4535,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4559,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4567,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4603,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4635,7 +4673,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4648,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4660,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4702,7 +4740,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4720,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4733,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4746,7 +4784,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4777,7 +4815,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4789,17 +4827,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4812,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4821,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>382</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>379</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>385</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4989,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5013,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5022,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5044,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>264</v>
+        <v>414</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5089,124 +5127,160 @@
         <v>0.39179751921654271</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>4.486903977417577</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>29.323920917327179</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>33.810824894744755</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-4.1459154780200791E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>394</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>395</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>397</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5223,9 +5297,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5754,7 +5839,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>4184</v>
@@ -5790,7 +5875,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-1023</v>
@@ -5826,7 +5911,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-3008</v>
@@ -5884,7 +5969,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7115,7 +7200,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7718,7 +7803,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8484,13 +8569,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8498,7 +8583,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8651,7 +8736,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>138</v>
@@ -8674,7 +8759,7 @@
         <v>2.7240755422739934E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8696,7 +8781,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8763,7 +8848,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8775,7 +8860,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8786,12 +8871,12 @@
         <v>-1928.2849984847301</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8802,12 +8887,12 @@
         <v>0.69180645031635546</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8815,12 +8900,12 @@
         <v>1928.2849984847301</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8828,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8904,7 +8989,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8915,15 +9000,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8940,7 +9025,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8974,7 +9059,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9845,7 +9930,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9870,7 +9955,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10198,7 +10283,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10258,7 +10343,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10382,7 +10467,7 @@
         <v>-3654</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10440,7 +10525,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10748,7 +10833,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10887,7 +10972,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10942,7 +11027,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11075,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11102,7 +11187,7 @@
         <v>4.5900649252604557E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11417,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11978,7 +12063,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12657,7 +12742,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13351,7 +13436,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13403,7 +13488,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13856,7 +13941,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13912,7 +13997,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14741,10 +14826,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14759,8 +14844,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14775,8 +14860,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14791,8 +14876,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14862,7 +14947,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14921,7 +15006,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14943,7 +15028,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14965,7 +15050,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14987,7 +15072,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15009,7 +15094,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15031,7 +15116,7 @@
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15053,7 +15138,7 @@
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15075,7 +15160,7 @@
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15097,7 +15182,7 @@
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15119,7 +15204,7 @@
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15141,7 +15226,7 @@
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15163,7 +15248,7 @@
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15185,7 +15270,7 @@
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15207,7 +15292,7 @@
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15229,7 +15314,7 @@
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15251,7 +15336,7 @@
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15273,7 +15358,7 @@
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15295,7 +15380,7 @@
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15317,7 +15402,7 @@
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15339,7 +15424,7 @@
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15361,7 +15446,7 @@
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
@@ -15383,7 +15468,7 @@
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
@@ -15405,7 +15490,7 @@
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
@@ -15427,7 +15512,7 @@
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
@@ -15449,7 +15534,7 @@
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
@@ -15471,7 +15556,7 @@
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
@@ -15493,7 +15578,7 @@
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
@@ -15515,7 +15600,7 @@
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
@@ -15537,7 +15622,7 @@
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
@@ -15559,7 +15644,7 @@
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
@@ -16137,7 +16222,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16189,7 +16274,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16209,7 +16294,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16263,7 +16348,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16276,7 +16361,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16286,11 +16371,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz Company(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16311,8 +16396,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16333,8 +16418,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16344,8 +16429,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16356,10 +16441,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16377,8 +16462,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16395,8 +16480,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16413,8 +16498,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16430,7 +16515,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16440,25 +16525,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16468,12 +16553,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16483,8 +16568,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16504,8 +16589,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16515,8 +16600,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16530,8 +16615,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16541,8 +16626,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16562,8 +16647,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16573,8 +16658,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16588,8 +16673,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16599,8 +16684,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16620,8 +16705,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16631,8 +16716,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16646,8 +16731,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16658,8 +16743,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16721,8 +16806,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16732,8 +16817,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16747,8 +16832,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16758,12 +16843,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -16779,8 +16864,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16790,8 +16875,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16805,8 +16890,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16816,8 +16901,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16832,7 +16917,7 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16841,7 +16926,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16850,10 +16935,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16866,7 +16951,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16874,11 +16959,11 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>4.2826760003620575E-2</v>
+        <v>4.2826760003620602E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16894,20 +16979,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16917,19 +17002,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16939,14 +17024,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16969,7 +17054,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16992,12 +17077,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17051,12 +17136,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17069,7 +17154,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17079,43 +17164,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>411</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>4.486903977417577</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>29.323920917327179</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>33.810824894744755</v>
+      </c>
+      <c r="D93" t="s">
+        <v>409</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-4.1459154780200791E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>335</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>336</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>337</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>336</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>337</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>336</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>339</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>337</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>340</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C32A89-AA3D-4690-BBA8-811BBAFBD32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B57890-8859-4DC4-BBF6-57115A7A3C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2313,31 +2309,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,6 +3739,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4108,7 +4125,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,10 +4204,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4213,19 +4230,19 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (USD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>19.745207945921621</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>349</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,537 +4768,577 @@
         <v>USD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>417</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>0.78990369994931575</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>0.40281804358844397</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>3.955391512509995</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>1334</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>-594.28499848473007</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>0</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="1" t="str">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>14.592547258724681</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>-26.938493611476797</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>369</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>62.43 USD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>30</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>43.96 USD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>30</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>30.87 USD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>30</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>21.47 USD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>14.59 USD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>32.464859269378167</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>382</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>417</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>415</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>1.6</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>3.1232000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>16.62200794592162</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>19.745207945921621</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.39179751921654271</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.486903977417577</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>4.2986729145576428</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>29.323920917327179</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="C135" s="239">
+        <v>27.471377899298453</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>414</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>33.810824894744755</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>31.770050813856095</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-4.1459154780200791E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>2.1401862541798766E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>386</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>391</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>388</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>394</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5290,24 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5839,7 +5896,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" s="181">
         <v>4184</v>
@@ -5875,7 +5932,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C23" s="181">
         <v>-1023</v>
@@ -5911,7 +5968,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C24" s="181">
         <v>-3008</v>
@@ -5969,7 +6026,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7200,7 +7257,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8575,7 +8632,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8583,7 +8640,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8736,7 +8793,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>138</v>
@@ -8759,7 +8816,7 @@
         <v>2.7240755422739934E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8781,7 +8838,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8848,7 +8905,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8860,7 +8917,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8871,12 +8928,12 @@
         <v>-1928.2849984847301</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8887,12 +8944,12 @@
         <v>0.69180645031635546</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8900,12 +8957,12 @@
         <v>1928.2849984847301</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8913,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8989,7 +9046,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9000,15 +9057,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>298</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9025,7 +9082,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9059,7 +9116,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9930,7 +9987,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9955,7 +10012,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10283,7 +10340,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10343,7 +10400,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10467,7 +10524,7 @@
         <v>-3654</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10525,7 +10582,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10833,7 +10890,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10972,7 +11029,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11027,7 +11084,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11160,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11187,7 +11244,7 @@
         <v>4.5900649252604557E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11502,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12063,7 +12120,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12742,7 +12799,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13436,7 +13493,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13488,7 +13545,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13997,7 +14054,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14826,10 +14883,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14844,8 +14901,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14860,8 +14917,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14876,8 +14933,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16222,7 +16279,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16294,7 +16351,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16348,7 +16405,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16361,7 +16418,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16371,11 +16428,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz Company(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16396,8 +16453,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16418,8 +16475,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16429,8 +16486,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16441,10 +16498,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>279</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16462,8 +16519,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16480,8 +16537,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16498,8 +16555,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16515,7 +16572,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16525,25 +16582,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>341</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>312</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>311</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16553,12 +16610,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16568,8 +16625,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16589,8 +16646,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16600,8 +16657,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16615,8 +16672,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16626,8 +16683,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16647,8 +16704,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16658,8 +16715,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16673,8 +16730,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16684,8 +16741,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16705,8 +16762,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16716,8 +16773,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16731,8 +16788,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16743,8 +16800,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16806,8 +16863,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16817,8 +16874,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16832,8 +16889,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16843,12 +16900,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -16864,8 +16921,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16875,8 +16932,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16890,8 +16947,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16901,8 +16958,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16917,7 +16974,7 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16926,7 +16983,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16935,10 +16992,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16951,7 +17008,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16963,7 +17020,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16979,20 +17036,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17002,19 +17059,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17024,14 +17081,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17054,7 +17111,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17077,15 +17134,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17136,12 +17193,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17154,7 +17211,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17166,16 +17223,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17184,7 +17241,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.486903977417577</v>
+        <v>4.2986729145576428</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17194,27 +17251,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>29.323920917327179</v>
+        <v>27.471377899298453</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>33.810824894744755</v>
+        <v>31.770050813856095</v>
       </c>
       <c r="D93" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-4.1459154780200791E-2</v>
+        <v>2.1401862541798766E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17222,7 +17279,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17230,30 +17287,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>335</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>336</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B57890-8859-4DC4-BBF6-57115A7A3C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F56EAC-B531-48C8-BEE2-CF85DA101D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1413,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1578,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1789,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2353,23 +2342,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>The Kraft Heinz Company</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KHC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>USD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CNS_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2377,26 +2380,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3071,7 +3074,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3113,23 +3116,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3138,13 +3141,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3215,10 +3218,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3229,7 +3232,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,7 +3270,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3277,7 +3280,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3288,29 +3291,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3326,7 +3329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,38 +3343,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3391,17 +3394,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3416,11 +3419,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3429,51 +3432,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3489,7 +3492,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3523,21 +3526,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3546,7 +3549,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3556,13 +3559,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3573,7 +3576,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3592,9 +3595,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3603,23 +3606,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3637,13 +3640,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3651,7 +3654,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3688,7 +3691,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3710,21 +3713,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3735,7 +3738,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3743,30 +3746,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4057,7 +4060,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4067,7 +4070,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4076,13 +4079,13 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
         <v>268</v>
       </c>
@@ -4096,7 +4099,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>KHC Stock Information</v>
@@ -4106,9 +4109,9 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
         <v>421</v>
@@ -4117,7 +4120,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>95</v>
       </c>
@@ -4129,7 +4132,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4139,9 +4142,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4149,7 +4152,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
         <v>269</v>
       </c>
@@ -4160,7 +4163,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (USD):</v>
@@ -4172,29 +4175,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4202,9 +4205,9 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>423</v>
@@ -4212,7 +4215,7 @@
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4225,7 +4228,7 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
@@ -4234,7 +4237,7 @@
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>277</v>
       </c>
@@ -4242,13 +4245,13 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (USD):</v>
@@ -4258,15 +4261,15 @@
         <v>19.745207945921621</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4275,13 +4278,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4289,43 +4292,43 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
         <v>231</v>
       </c>
       <c r="C28" s="108">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
         <v>233</v>
       </c>
@@ -4338,20 +4341,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
         <v>235</v>
       </c>
@@ -4364,7 +4367,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
         <v>236</v>
       </c>
@@ -4377,16 +4380,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
         <v>238</v>
       </c>
@@ -4399,18 +4402,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4423,9 +4426,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4438,7 +4441,7 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
         <v>239</v>
       </c>
@@ -4451,12 +4454,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
         <v>266</v>
       </c>
@@ -4469,16 +4472,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
         <v>240</v>
       </c>
@@ -4491,16 +4494,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
         <v>243</v>
       </c>
@@ -4513,25 +4516,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
         <v>271</v>
       </c>
@@ -4544,7 +4547,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
         <v>249</v>
       </c>
@@ -4557,27 +4560,27 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.8134932571433455E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.5536272127733433E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4585,66 +4588,66 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
         <v>248</v>
       </c>
@@ -4653,34 +4656,34 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
         <v>252</v>
       </c>
@@ -4688,12 +4691,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
         <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.739592592287465</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4701,9 +4704,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4711,38 +4714,38 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
         <v>256</v>
       </c>
@@ -4755,12 +4758,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
         <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>16.649068991502919</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4768,39 +4771,39 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
         <v>265</v>
       </c>
@@ -4813,7 +4816,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
         <v>267</v>
       </c>
@@ -4826,12 +4829,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
         <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4839,12 +4842,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6">
       <c r="B98" s="47" t="s">
         <v>258</v>
       </c>
@@ -4857,12 +4860,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
         <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4870,16 +4873,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
         <v>283</v>
       </c>
@@ -4892,9 +4895,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4905,9 +4908,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4915,16 +4918,16 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
         <v>118</v>
       </c>
@@ -4941,7 +4944,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4963,7 +4966,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4985,7 +4988,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5007,7 +5010,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5029,7 +5032,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5051,7 +5054,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
         <v>259</v>
       </c>
@@ -5064,18 +5067,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5083,30 +5086,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
@@ -5115,7 +5118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
         <v>278</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
         <v>262</v>
       </c>
@@ -5137,12 +5140,19 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5152,7 +5162,7 @@
         <v>3.1232000000000002</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5162,7 +5172,7 @@
         <v>16.62200794592162</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
@@ -5175,7 +5185,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5184,56 +5194,63 @@
         <v>0.39179751921654271</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.2986729145576428</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4.276819119138624</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>27.471377899298453</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>27.258121863499866</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>31.770050813856095</v>
+        <v>31.534940982638489</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>2.1401862541798766E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>2.8643841608049225E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5241,103 +5258,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="344" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
       <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
+        <v>391</v>
+      </c>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5354,17 +5382,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5389,7 +5406,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5397,7 +5414,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
@@ -5446,7 +5463,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5462,7 +5479,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5470,7 +5487,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5506,7 +5523,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -5542,7 +5559,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -5578,7 +5595,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -5594,7 +5611,7 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -5610,7 +5627,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -5626,7 +5643,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -5642,7 +5659,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -5658,7 +5675,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5694,7 +5711,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -5710,7 +5727,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -5746,7 +5763,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -5782,7 +5799,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -5818,13 +5835,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -5842,7 +5859,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -5868,7 +5885,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -5894,9 +5911,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>4184</v>
@@ -5930,9 +5947,9 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-1023</v>
@@ -5966,9 +5983,9 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-3008</v>
@@ -6002,7 +6019,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (USD)</v>
@@ -6021,15 +6038,15 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6056,7 +6073,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6083,7 +6100,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6102,7 +6119,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6121,7 +6138,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6140,7 +6157,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6156,12 +6173,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6210,7 +6227,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6259,7 +6276,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6308,7 +6325,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6357,7 +6374,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6406,7 +6423,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6455,7 +6472,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6504,7 +6521,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -6553,7 +6570,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -6602,7 +6619,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -6651,7 +6668,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -6700,7 +6717,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -6749,7 +6766,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -6798,12 +6815,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6852,7 +6869,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -6901,12 +6918,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -6955,7 +6972,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7004,7 +7021,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7053,7 +7070,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7102,13 +7119,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7157,7 +7174,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7206,7 +7223,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7255,9 +7272,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7304,7 +7321,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7353,12 +7370,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7408,7 +7425,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7457,7 +7474,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7507,7 +7524,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -7556,7 +7573,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7606,7 +7623,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -7622,13 +7639,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7677,7 +7694,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -7711,7 +7728,7 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -7745,7 +7762,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7794,7 +7811,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7875,7 +7892,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7886,7 +7903,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7898,11 +7915,11 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -7913,7 +7930,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -7933,7 +7950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7954,7 +7971,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7975,7 +7992,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7996,7 +8013,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8017,7 +8034,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8038,7 +8055,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8059,7 +8076,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8071,7 +8088,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8083,7 +8100,7 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8107,12 +8124,12 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8132,7 +8149,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8152,7 +8169,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8172,7 +8189,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8192,7 +8209,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8212,7 +8229,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8232,7 +8249,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8252,7 +8269,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8272,7 +8289,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8284,7 +8301,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8297,7 +8314,7 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8321,7 +8338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8338,7 +8355,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8357,7 +8374,7 @@
         <v>-32014.400000000001</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8372,7 +8389,7 @@
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8391,7 +8408,7 @@
         <v>-32148.400000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8407,7 +8424,7 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8424,7 +8441,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8444,7 +8461,7 @@
         <v>6947.6</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8455,7 +8472,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
@@ -8468,7 +8485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -8487,7 +8504,7 @@
         <v>5747</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8503,7 +8520,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8519,7 +8536,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8535,7 +8552,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8554,7 +8571,7 @@
         <v>715.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -8574,7 +8591,7 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8594,7 +8611,7 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8613,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -8624,7 +8641,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -8632,13 +8649,13 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -8652,7 +8669,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (USD)</v>
@@ -8667,10 +8684,10 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -8683,7 +8700,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -8697,7 +8714,7 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -8708,10 +8725,10 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -8723,7 +8740,7 @@
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -8737,7 +8754,7 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -8751,10 +8768,10 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -8766,7 +8783,7 @@
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -8777,7 +8794,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -8788,10 +8805,10 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -8803,7 +8820,7 @@
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -8819,7 +8836,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -8830,7 +8847,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -8838,13 +8855,13 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -8860,7 +8877,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -8870,7 +8887,7 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -8880,7 +8897,7 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -8890,7 +8907,7 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -8900,12 +8917,12 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8915,9 +8932,9 @@
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8928,12 +8945,12 @@
         <v>-1928.2849984847301</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8944,12 +8961,12 @@
         <v>0.69180645031635546</v>
       </c>
       <c r="F74" s="283" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
+      <c r="B75" s="80" t="s">
         <v>328</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="80" t="s">
-        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8957,12 +8974,12 @@
         <v>1928.2849984847301</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8970,13 +8987,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -8988,7 +9005,7 @@
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9002,7 +9019,7 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9016,7 +9033,7 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9030,7 +9047,7 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9044,9 +9061,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9055,24 +9072,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
       </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-19869</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-16.649068991502919</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9080,16 +9097,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>-594.28499848473007</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9097,7 +9114,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
         <v>190</v>
       </c>
@@ -9106,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9114,9 +9131,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9145,7 +9162,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9157,7 +9174,7 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
@@ -9214,7 +9231,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9237,13 +9254,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9251,7 +9268,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9308,7 +9325,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9363,7 +9380,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9418,7 +9435,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -9473,7 +9490,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -9530,7 +9547,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -9585,7 +9602,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -9640,7 +9657,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -9697,7 +9714,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -9752,7 +9769,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -9807,7 +9824,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -9862,7 +9879,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -9919,7 +9936,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -9976,7 +9993,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -9987,7 +10004,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10002,7 +10019,7 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10012,7 +10029,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10027,7 +10044,7 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10084,7 +10101,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10103,7 +10120,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10126,7 +10143,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10147,7 +10164,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10204,7 +10221,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10261,7 +10278,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10318,18 +10335,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10340,7 +10357,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10388,7 +10405,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10400,7 +10417,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10448,7 +10465,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -10503,18 +10520,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -10524,7 +10541,7 @@
         <v>-3654</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10571,7 +10588,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -10582,7 +10599,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10630,7 +10647,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -10687,18 +10704,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10756,7 +10773,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10814,7 +10831,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -10869,18 +10886,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -10890,7 +10907,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10938,10 +10955,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -10964,14 +10981,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11026,10 +11043,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11081,10 +11098,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11138,7 +11155,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11193,11 +11210,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11207,7 +11224,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11217,7 +11234,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11234,7 +11251,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11244,7 +11261,7 @@
         <v>4.5900649252604557E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11261,7 +11278,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11316,11 +11333,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11330,7 +11347,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11385,7 +11402,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11440,7 +11457,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -11495,7 +11512,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -11550,7 +11567,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -11559,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11606,7 +11623,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -11661,11 +11678,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -11675,7 +11692,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -11700,7 +11717,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -11725,7 +11742,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -11750,7 +11767,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -11777,10 +11794,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -11788,7 +11805,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>427</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11803,7 +11820,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -11824,7 +11841,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -11881,7 +11898,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -11938,7 +11955,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -11995,7 +12012,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12052,7 +12069,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12109,7 +12126,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12120,7 +12137,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>428</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12168,7 +12185,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12225,7 +12242,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12282,7 +12299,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12339,7 +12356,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12396,7 +12413,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12454,7 +12471,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -12511,7 +12528,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -12537,7 +12554,7 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -12561,7 +12578,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -12618,18 +12635,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12685,19 +12702,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (USD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>1909.4401024000001</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1909.4401024000001</v>
       </c>
       <c r="H91" s="74">
@@ -12741,18 +12758,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.63012781093037351</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.74938779529042387</v>
       </c>
       <c r="H92" s="171">
@@ -12796,10 +12813,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12851,11 +12868,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -12876,7 +12893,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -12933,7 +12950,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -12990,10 +13007,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13016,7 +13033,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13026,7 +13043,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13083,7 +13100,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13140,7 +13157,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13197,7 +13214,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13254,7 +13271,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13311,11 +13328,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13338,7 +13355,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13395,7 +13412,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13452,7 +13469,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -13479,21 +13496,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13542,10 +13559,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13594,11 +13611,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13652,7 +13669,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -13707,7 +13724,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -13761,7 +13778,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -13817,7 +13834,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -13874,7 +13891,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13893,7 +13910,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -13916,7 +13933,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -13937,7 +13954,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13995,7 +14012,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14052,9 +14069,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14102,688 +14119,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14805,7 +14822,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14814,7 +14831,7 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -14826,12 +14843,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
@@ -14839,7 +14856,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -14860,7 +14877,7 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
         <v>124</v>
       </c>
@@ -14871,7 +14888,7 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
@@ -14889,7 +14906,7 @@
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -14905,7 +14922,7 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -14921,7 +14938,7 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
         <v>191</v>
       </c>
@@ -14937,7 +14954,7 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
@@ -14951,7 +14968,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
         <v>167</v>
       </c>
@@ -14965,12 +14982,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>14.592547258724681</v>
       </c>
       <c r="D12" t="str">
@@ -14979,10 +14996,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -14992,13 +15009,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15008,7 +15025,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15018,12 +15035,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>32.46666798264237</v>
       </c>
       <c r="D18" t="str">
@@ -15032,10 +15049,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15053,7 +15070,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15075,7 +15092,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15097,7 +15114,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15119,7 +15136,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15141,7 +15158,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15163,7 +15180,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15185,7 +15202,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15207,7 +15224,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15229,7 +15246,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15251,7 +15268,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15273,7 +15290,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15295,7 +15312,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15317,7 +15334,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15339,7 +15356,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15361,7 +15378,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15383,7 +15400,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15405,7 +15422,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15427,7 +15444,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15449,7 +15466,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15471,7 +15488,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15493,7 +15510,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15515,7 +15532,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15537,7 +15554,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15559,7 +15576,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15581,7 +15598,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15603,7 +15620,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15625,7 +15642,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15647,7 +15664,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15669,7 +15686,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15691,7 +15708,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15713,7 +15730,7 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
@@ -15735,7 +15752,7 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
@@ -15746,11 +15763,11 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -15760,7 +15777,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>59209.008646836883</v>
@@ -15787,7 +15804,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15809,7 +15826,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15830,7 +15847,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15851,7 +15868,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15872,7 +15889,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15893,7 +15910,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15914,14 +15931,14 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -15931,7 +15948,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -15954,7 +15971,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15980,7 +15997,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16007,7 +16024,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16034,7 +16051,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16061,7 +16078,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16088,7 +16105,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16114,7 +16131,7 @@
         <v>51.337452569176612</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16140,7 +16157,7 @@
         <v>62.434508619809236</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16157,7 +16174,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16179,7 +16196,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16202,7 +16219,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16225,7 +16242,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16248,7 +16265,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16270,38 +16287,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16332,7 +16349,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16342,7 +16359,7 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -16351,11 +16368,11 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -16367,7 +16384,7 @@
         <v>-28.81</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -16387,7 +16404,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16396,7 +16413,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -16416,7 +16433,7 @@
         <v>34.064859269378168</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -16441,7 +16458,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -16463,7 +16480,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -16485,7 +16502,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16496,7 +16513,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
@@ -16510,7 +16527,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -16529,7 +16546,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -16547,7 +16564,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -16558,7 +16575,7 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -16567,15 +16584,15 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -16583,22 +16600,22 @@
         <v>30</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>280</v>
       </c>
@@ -16613,7 +16630,7 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>281</v>
       </c>
@@ -16628,7 +16645,7 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -16637,7 +16654,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -16649,7 +16666,7 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -16660,7 +16677,7 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
@@ -16675,7 +16692,7 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -16686,7 +16703,7 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -16695,7 +16712,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -16707,7 +16724,7 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -16718,7 +16735,7 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
@@ -16733,7 +16750,7 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -16744,7 +16761,7 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -16753,7 +16770,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -16765,7 +16782,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -16776,7 +16793,7 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
@@ -16791,7 +16808,7 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -16803,7 +16820,7 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
@@ -16816,7 +16833,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -16825,12 +16842,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -16840,12 +16857,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -16854,7 +16871,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -16866,7 +16883,7 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -16877,7 +16894,7 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
@@ -16892,7 +16909,7 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -16903,16 +16920,16 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -16924,7 +16941,7 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -16935,7 +16952,7 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
@@ -16950,7 +16967,7 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -16961,7 +16978,7 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
@@ -16974,31 +16991,31 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -17008,10 +17025,10 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -17020,10 +17037,10 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
@@ -17036,20 +17053,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
+      <c r="B68" s="109" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="282" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B68" s="109" t="s">
-        <v>360</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17057,21 +17074,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17079,23 +17096,23 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>-0.52817248309270792</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -17104,14 +17121,14 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17119,7 +17136,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -17132,21 +17149,21 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
@@ -17158,7 +17175,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
@@ -17168,7 +17185,7 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
@@ -17188,17 +17205,17 @@
         <v>0.39179751921654271</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17209,108 +17226,108 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>9.408289080523935E-2</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.2986729145576428</v>
+        <v>4.276819119138624</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>27.471377899298453</v>
+        <v>27.258121863499866</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>31.770050813856095</v>
+        <v>31.534940982638489</v>
       </c>
       <c r="D93" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>2.1401862541798766E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2.8643841608049225E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F56EAC-B531-48C8-BEE2-CF85DA101D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BDCCF1-A91D-47A4-A0BD-887925123D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BDCCF1-A91D-47A4-A0BD-887925123D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B30B22D-3F28-4B0B-AF87-547AFD25755C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3747,29 +3747,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4180,13 +4180,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4293,22 +4293,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4320,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4346,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4381,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4403,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4473,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4495,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4517,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4593,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4666,22 +4666,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4718,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4874,13 +4874,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4919,13 +4919,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,13 +5068,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5087,22 +5087,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.276819119138624</v>
+        <v>4.1233551795966088</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>27.258121863499866</v>
+        <v>25.771651988214895</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>31.534940982638489</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>2.8643841608049225E-2</v>
+        <v>7.9157962159738249E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5259,13 +5259,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5302,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5316,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,17 +5355,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5382,6 +5371,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17248,8 +17248,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.276819119138624</v>
+        <v>4.1233551795966088</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>27.258121863499866</v>
+        <v>25.771651988214895</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>31.534940982638489</v>
+        <v>29.895007167811503</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>2.8643841608049225E-2</v>
+        <v>7.9157962159738249E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B30B22D-3F28-4B0B-AF87-547AFD25755C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF96C725-AD3D-4249-AB56-246FD1E612C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3739,37 +3744,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4082,7 +4087,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4114,10 +4119,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4128,7 +4133,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4180,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4210,7 +4215,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4233,7 +4238,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4245,10 +4250,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4269,7 +4274,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4293,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4632,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4644,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4666,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4772,28 +4777,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
@@ -4874,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4896,8 +4901,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4919,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,17 +5073,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5087,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5142,14 +5147,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5196,14 +5201,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5212,7 +5217,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>4.1233551795966088</v>
       </c>
     </row>
@@ -5222,16 +5227,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>25.771651988214895</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5244,7 +5249,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>7.9157962159738249E-2</v>
       </c>
     </row>
@@ -5259,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,6 +5360,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5371,17 +5387,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6043,7 +6048,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8649,7 +8654,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11805,7 +11810,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12137,7 +12142,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16348,7 +16353,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17240,16 +17245,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17258,9 +17263,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.1233551795966088</v>
+        <v>3.3703703703703702</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17268,69 +17275,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>25.771651988214895</v>
+        <v>18.787534299408662</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>29.895007167811503</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>22.157904669779033</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>7.9157962159738249E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.31748034125381119</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>4.1233551795966088</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>25.771651988214895</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>29.895007167811503</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>7.9157962159738249E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF96C725-AD3D-4249-AB56-246FD1E612C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FC0D2E-50B4-43FB-98CD-7134962C2C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3752,29 +3752,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4185,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4247,7 +4247,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>19.745207945921621</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4298,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4598,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4671,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4723,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4879,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4924,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5073,13 +5073,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5092,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>3.1232000000000002</v>
+        <v>2.9057806099226227</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>16.62200794592162</v>
+        <v>14.776904537723331</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>19.745207945921621</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39179751921654271</v>
+        <v>0.45532845219123441</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5264,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5307,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5321,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5360,17 +5360,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5387,6 +5376,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.1232000000000002</v>
+        <v>2.9057806099226227</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>16.62200794592162</v>
+        <v>14.776904537723331</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>19.745207945921621</v>
+        <v>17.682685147645955</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39179751921654271</v>
+        <v>0.45532845219123441</v>
       </c>
     </row>
     <row r="84" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FC0D2E-50B4-43FB-98CD-7134962C2C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D34118B-C348-4886-B9FE-9E5493ACE042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3752,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,7 +4066,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4087,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4119,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4133,7 +4135,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4185,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4215,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4238,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4250,7 +4252,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4298,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4598,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4637,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4649,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4671,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4723,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4778,7 +4780,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4796,7 +4798,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4879,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4902,7 +4904,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4924,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5073,17 +5075,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5092,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5145,19 +5147,19 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5167,7 +5169,7 @@
         <v>2.9057806099226227</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5177,7 +5179,7 @@
         <v>14.776904537723331</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
@@ -5190,7 +5192,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5199,167 +5201,232 @@
         <v>0.45532845219123441</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>4.1233551795966088</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>3.3703703703703702</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
+        <f>Scenarios!C92</f>
+        <v>18.787534299408662</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" s="239">
+        <f>Scenarios!C93</f>
+        <v>22.157904669779033</v>
+      </c>
+      <c r="D139" s="47" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.31748034125381119</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>4.1233551795966088</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
         <f>Scenarios!C98</f>
         <v>25.771651988214895</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
-      <c r="B139" s="80" t="s">
-        <v>410</v>
-      </c>
-      <c r="C139" s="239">
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
         <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D139" s="101" t="str">
+      <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="238" t="s">
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
         <v>7.9157962159738249E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5376,20 +5443,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -6048,7 +6104,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8654,7 +8710,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11810,7 +11866,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12142,7 +12198,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17245,12 +17301,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17308,7 +17364,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D34118B-C348-4886-B9FE-9E5493ACE042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484961B7-5DCB-4153-9CF8-25C0CD22679E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484961B7-5DCB-4153-9CF8-25C0CD22679E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C595D8-716E-41D8-BBB0-819D58427CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3754,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4089,7 +4092,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4121,10 +4124,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4135,7 +4138,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4187,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4217,7 +4220,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4240,7 +4243,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4300,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4600,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4639,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4673,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5149,7 +5152,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5203,14 +5206,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5264,7 +5267,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5320,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6104,7 +6107,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11866,7 +11869,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12198,7 +12201,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17301,12 +17304,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C595D8-716E-41D8-BBB0-819D58427CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62471A78-DC05-4DB8-A8F2-8B6BF144ED07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2356,9 +2356,6 @@
   </si>
   <si>
     <t>@ Entry Yield</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>The Kraft Heinz Company</t>
@@ -3757,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4092,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4124,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>424</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4138,7 +4135,7 @@
         <v>28.81</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4190,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4220,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4243,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4303,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4603,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4642,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4654,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4676,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4728,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4884,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4929,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5078,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5323,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6107,7 +6104,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11869,7 +11866,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12201,7 +12198,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62471A78-DC05-4DB8-A8F2-8B6BF144ED07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58B77FD-D40D-4BBE-BFC2-48F94B4A6F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>28.81</v>
+        <v>28.4</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>426</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>34381.85584384</v>
+        <v>33892.561817599999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.408289080523935E-2</v>
+        <v>9.9596254590427646E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.8134932571433455E-2</v>
+        <v>8.9407303076866118E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.5536272127733433E-2</v>
+        <v>5.6338028169014093E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.5536272127733433E-2</v>
+        <v>5.6338028169014093E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.5536272127733433E-2</v>
+        <v>5.6338028169014093E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14080,50 +14080,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.8134932571433455E-2</v>
+        <v>8.9407303076866118E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.4108855891108355E-2</v>
+        <v>7.5178737261367312E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8960791725988194E-2</v>
+        <v>6.9956352451609846E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.1906363780434009E-2</v>
+        <v>3.236698382092619E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-5.7879365472254954E-3</v>
+        <v>-5.8714947861114967E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.4576916494500219E-2</v>
+        <v>-2.4931724091779975E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.8532491220242266E-2</v>
+        <v>2.8944403945604918E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.30356127509242459</v>
+        <v>-0.30794367378213916</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.31990710594438809</v>
+        <v>0.32452548317809227</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10520083663977195</v>
+        <v>0.10671958111238837</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.7310916672586633E-2</v>
+        <v>2.7705193990747216E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14137,43 +14137,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9867707330056339E-2</v>
+        <v>8.102072704855362E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2776218157807849E-2</v>
+        <v>8.3971226941071966E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8873536401155649E-2</v>
+        <v>6.9867837454834297E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9783150876175415E-2</v>
+        <v>3.0213118899387804E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0499724088182935E-2</v>
+        <v>1.0651304611991208E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6221514300436599E-2</v>
+        <v>5.7033162922379518E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.29823870027763938</v>
+        <v>-0.30254425897883064</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.31964533996989042</v>
+        <v>0.32425993818776561</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10592796434670983</v>
+        <v>0.10745720608551795</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8818065055552238E-2</v>
+        <v>1.9089734304593663E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-28.81</v>
+        <v>-28.4</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>28.81</v>
+        <v>28.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>28.81</v>
+        <v>28.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.408289080523935E-2</v>
+        <v>9.9596254590427646E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58B77FD-D40D-4BBE-BFC2-48F94B4A6F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A14D5F-7C8B-4D18-A7DD-441545834B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>28.4</v>
+        <v>28.23</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>426</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>33892.561817599999</v>
+        <v>33689.683806720001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.9596254590427646E-2</v>
+        <v>0.10191457699731421</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.9407303076866118E-2</v>
+        <v>8.9945710498866363E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.6338028169014093E-2</v>
+        <v>5.6677293659227773E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.6338028169014093E-2</v>
+        <v>5.6677293659227773E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.6338028169014093E-2</v>
+        <v>5.6677293659227773E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14080,50 +14080,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9407303076866118E-2</v>
+        <v>8.9945710498866363E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.5178737261367312E-2</v>
+        <v>7.5631460794290881E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.9956352451609846E-2</v>
+        <v>7.037762697930286E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.236698382092619E-2</v>
+        <v>3.2561896582157412E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-5.8714947861114967E-3</v>
+        <v>-5.9068527072464226E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.4931724091779975E-2</v>
+        <v>-2.5081861998106671E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.8944403945604918E-2</v>
+        <v>2.9118706059340402E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.30794367378213916</v>
+        <v>-0.30979809902276839</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.32452548317809227</v>
+        <v>0.32647976345227842</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10671958111238837</v>
+        <v>0.10736224242266489</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.7705193990747216E-2</v>
+        <v>2.787203362866528E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14137,43 +14137,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.102072704855362E-2</v>
+        <v>8.1508630824616457E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3971226941071966E-2</v>
+        <v>8.4476898516700094E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9867837454834297E-2</v>
+        <v>7.0288578948540348E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0213118899387804E-2</v>
+        <v>3.0395061166936365E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0651304611991208E-2</v>
+        <v>1.0715446368421902E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7033162922379518E-2</v>
+        <v>5.7376614487976554E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30254425897883064</v>
+        <v>-0.30436616914625536</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.32425993818776561</v>
+        <v>0.32621261935999085</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10745720608551795</v>
+        <v>0.10810430934568578</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9089734304593663E-2</v>
+        <v>1.9204691967781084E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-28.4</v>
+        <v>-28.23</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>28.4</v>
+        <v>28.23</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>28.4</v>
+        <v>28.23</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.9596254590427646E-2</v>
+        <v>0.10191457699731421</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A14D5F-7C8B-4D18-A7DD-441545834B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47BA0B5-9427-45B7-9A6E-D9FF0C92EC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>28.23</v>
+        <v>28.49</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>426</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>33689.683806720001</v>
+        <v>33999.967823359999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10191457699731421</v>
+        <v>9.8376640230496193E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.9945710498866363E-2</v>
+        <v>8.9124865124008343E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.6677293659227773E-2</v>
+        <v>5.616005616005617E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.6677293659227773E-2</v>
+        <v>5.616005616005617E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.6677293659227773E-2</v>
+        <v>5.616005616005617E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14080,50 +14080,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9945710498866363E-2</v>
+        <v>8.9124865124008343E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.5631460794290881E-2</v>
+        <v>7.4941247392868782E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.037762697930286E-2</v>
+        <v>6.9735360113222872E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2561896582157412E-2</v>
+        <v>3.2264736416788481E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-5.9068527072464226E-3</v>
+        <v>-5.8529467155341002E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.5081861998106671E-2</v>
+        <v>-2.485296469661465E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.9118706059340402E-2</v>
+        <v>2.8852968482105289E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.30979809902276839</v>
+        <v>-0.30697087874386636</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.32647976345227842</v>
+        <v>0.32350030615155567</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10736224242266489</v>
+        <v>0.10638245361852684</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.787203362866528E-2</v>
+        <v>2.7617673195409649E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14137,43 +14137,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1508630824616457E-2</v>
+        <v>8.076478231586251E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4476898516700094E-2</v>
+        <v>8.3705961569899748E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0288578948540348E-2</v>
+        <v>6.9647124735601765E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0395061166936365E-2</v>
+        <v>3.0117675561341303E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0715446368421902E-2</v>
+        <v>1.0617657107074423E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7376614487976554E-2</v>
+        <v>5.6852994980539785E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30436616914625536</v>
+        <v>-0.30158852070897824</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.32621261935999085</v>
+        <v>0.32323560001869228</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10810430934568578</v>
+        <v>0.10711774843203616</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9204691967781084E-2</v>
+        <v>1.9029429773620921E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-28.23</v>
+        <v>-28.49</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>28.23</v>
+        <v>28.49</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>28.23</v>
+        <v>28.49</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10191457699731421</v>
+        <v>9.8376640230496193E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47BA0B5-9427-45B7-9A6E-D9FF0C92EC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46CFF4A-3A9E-41E1-B1FF-C88C567D4157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,19 +2358,40 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>The Kraft Heinz Company</t>
   </si>
   <si>
     <t>KHC</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>USD</t>
   </si>
   <si>
     <t>CNS_01</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -3053,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,6 +3775,13 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4066,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4089,7 +4116,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>KHC Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4121,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>1193400064</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>28.49</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>426</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>1193400064</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (USD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>33999.967823359999</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>USD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>426</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>USD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (USD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>17.682685147645955</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>9.8376640230496193E-2</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>5023.2701205832382</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>1164</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-1164</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-912</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-912</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-12.097342754012749</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-912</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-912</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-12.097342754012749</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-1068.9302313516419</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2548</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2548</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>3030.2425464775833</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.9124865124008343E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.616005616005617E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.739592592287465</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>19869</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>16.649068991502919</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>1334</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-594.28499848473007</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.49797634205986613</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4869,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-594.28499848473007</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-0.49797634205986613</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>14.592547258724681</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-26.938493611476797</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>14.592547258724681</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-26.938493611476797</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>62.43 USD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>30</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>43.96 USD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>30</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>30.87 USD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>30</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>21.47 USD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>14.59 USD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>32.464859269378167</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>1.6</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>KHC</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>2.9057806099226227</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>14.776904537723331</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>17.682685147645955</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.45532845219123441</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>3.3703703703703702</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>18.787534299408662</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>22.157904669779033</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.31748034125381119</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>4.1233551795966088</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>25.771651988214895</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>7.9157962159738249E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5477,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6104,7 +6227,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9238,7 +9361,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11866,7 +11989,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12198,7 +12321,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14933,7 +15056,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14943,7 +15066,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14961,10 +15084,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14979,8 +15102,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -14995,8 +15118,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15011,8 +15134,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15038,7 +15161,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>USD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16506,11 +16629,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz Company(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16531,8 +16654,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16553,8 +16676,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16564,8 +16687,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16578,8 +16701,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16597,8 +16720,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16615,8 +16738,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16633,8 +16756,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16660,21 +16783,21 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16688,8 +16811,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16703,8 +16826,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16724,8 +16847,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16735,8 +16858,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16750,8 +16873,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16761,8 +16884,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16782,8 +16905,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16793,8 +16916,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16808,8 +16931,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16819,8 +16942,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16840,8 +16963,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16851,8 +16974,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16866,8 +16989,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16878,8 +17001,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16941,8 +17064,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16952,8 +17075,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16967,8 +17090,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16978,8 +17101,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -16999,8 +17122,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17010,8 +17133,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17025,8 +17148,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17036,8 +17159,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17055,7 +17178,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17220,7 +17343,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17309,7 +17432,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17367,7 +17490,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46CFF4A-3A9E-41E1-B1FF-C88C567D4157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC4B950-D807-4DD2-B998-C384785E458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8568,7 +8568,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>134</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC4B950-D807-4DD2-B998-C384785E458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B66AAC-60BC-4F14-9C0C-95C659C75BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>28.49</v>
+        <v>27.17</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>33999.967823359999</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>17.682685147645955</v>
+        <v>14.373490987382715</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.8376640230496193E-2</v>
+        <v>0.11681748174457507</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.9124865124008343E-2</v>
+        <v>9.3454818085498617E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.616005616005617E-2</v>
+        <v>5.8888479941111523E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>2.9057806099226227</v>
+        <v>2.5422740524781333</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>14.776904537723331</v>
+        <v>11.831216934904582</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>17.682685147645955</v>
+        <v>14.373490987382715</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45532845219123441</v>
+        <v>0.55726002481272963</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13004,12 +13003,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.616005616005617E-2</v>
+        <v>5.8888479941111523E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.616005616005617E-2</v>
+        <v>5.8888479941111523E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14203,50 +14202,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9124865124008343E-2</v>
+        <v>9.3454818085498617E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.4941247392868782E-2</v>
+        <v>7.8582117711550659E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.9735360113222872E-2</v>
+        <v>7.3123312831274184E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2264736416788481E-2</v>
+        <v>3.3832253975498848E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-5.8529467155341002E-3</v>
+        <v>-6.1373004021187524E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.485296469661465E-2</v>
+        <v>-2.6060396179850984E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.8852968482105289E-2</v>
+        <v>3.0254732133057769E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.30697087874386636</v>
+        <v>-0.3218844437030825</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.32350030615155567</v>
+        <v>0.33921692021559879</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10638245361852684</v>
+        <v>0.11155083193197753</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.7617673195409649E-2</v>
+        <v>2.8959422500449791E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14260,43 +14259,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.076478231586251E-2</v>
+        <v>8.4688577408131127E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3705961569899748E-2</v>
+        <v>8.7772647961959646E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9647124735601765E-2</v>
+        <v>7.303079071465933E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0117675561341303E-2</v>
+        <v>3.1580882471204032E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0617657107074423E-2</v>
+        <v>1.1133494699320953E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6852994980539785E-2</v>
+        <v>5.9615083805505273E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30158852070897824</v>
+        <v>-0.31624059458957632</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.32323560001869228</v>
+        <v>0.33893935386575424</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10711774843203616</v>
+        <v>0.11232184957043466</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9029429773620921E-2</v>
+        <v>1.9953936483270516E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16565,7 +16564,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-28.49</v>
+        <v>-27.17</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16805,7 +16804,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>28.49</v>
+        <v>27.17</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17343,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17353,7 +17352,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.9057806099226227</v>
+        <v>2.5422740524781333</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17365,7 +17364,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>14.776904537723331</v>
+        <v>11.831216934904582</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17375,7 +17374,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>17.682685147645955</v>
+        <v>14.373490987382715</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17386,7 +17385,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45532845219123441</v>
+        <v>0.55726002481272963</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17403,7 +17402,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>28.49</v>
+        <v>27.17</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17416,7 +17415,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.8376640230496193E-2</v>
+        <v>0.11681748174457507</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B66AAC-60BC-4F14-9C0C-95C659C75BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0540E3-0590-4733-8CAC-893D7EFE089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>32424.679738880001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0540E3-0590-4733-8CAC-893D7EFE089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C62BAC8-A32E-405F-BA59-C89DFB4AC01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -7363,11 +7363,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-1164</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-1164</v>
       </c>
       <c r="E62" s="183">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C62BAC8-A32E-405F-BA59-C89DFB4AC01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD4BCCF-3255-49FE-9B61-C526F365ECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD4BCCF-3255-49FE-9B61-C526F365ECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919A13F-E6CB-4C20-9971-AE6D835C6BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>27.17</v>
+        <v>27.414999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4216,7 +4228,7 @@
         <v>425</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>32424.679738880001</v>
+        <v>32717.062754559996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4294,7 +4306,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11681748174457507</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.11330244753933805</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.3454818085498617E-2</v>
+        <v>9.2619639153127764E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8888479941111523E-2</v>
+        <v>5.8362210468721511E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5308,7 +5324,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5318,7 +5334,7 @@
         <v>3.3703703703703702</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5328,7 +5344,7 @@
         <v>18.787534299408662</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5363,12 +5379,12 @@
         <v>0.31748034125381119</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5387,7 +5403,7 @@
         <v>4.1233551795966088</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5397,7 +5413,7 @@
         <v>25.771651988214895</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
@@ -5410,7 +5426,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5432,118 +5448,187 @@
         <v>7.9157962159738249E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>3.8601650015018389</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>23.269525289089753</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>27.12969029059159</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.16438328980676686</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6227,7 +6312,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11989,7 +12074,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12321,7 +12406,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13004,12 +13089,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8888479941111523E-2</v>
+        <v>5.8362210468721511E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8888479941111523E-2</v>
+        <v>5.8362210468721511E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14203,50 +14288,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3454818085498617E-2</v>
+        <v>9.2619639153127764E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.8582117711550659E-2</v>
+        <v>7.7879851841066272E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.3123312831274184E-2</v>
+        <v>7.2469830735937255E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3832253975498848E-2</v>
+        <v>3.3529904815404118E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-6.1373004021187524E-3</v>
+        <v>-6.082453106896462E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.6060396179850984E-2</v>
+        <v>-2.5827501886067895E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.0254732133057769E-2</v>
+        <v>2.99843542606303E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.3218844437030825</v>
+        <v>-0.31900785465667525</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.33921692021559879</v>
+        <v>0.33618543579273463</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11155083193197753</v>
+        <v>0.11055393410876636</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.8959422500449791E-2</v>
+        <v>2.8700620439074263E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14260,43 +14345,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4688577408131127E-2</v>
+        <v>8.3931739856973303E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7772647961959646E-2</v>
+        <v>8.6988248955916239E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.303079071465933E-2</v>
+        <v>7.2378135462968965E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1580882471204032E-2</v>
+        <v>3.1298653173175768E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1133494699320953E-2</v>
+        <v>1.1033997847184035E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9615083805505273E-2</v>
+        <v>5.9082320882567145E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31624059458957632</v>
+        <v>-0.31341444300560967</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.33893935386575424</v>
+        <v>0.33591034997382979</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11232184957043466</v>
+        <v>0.1113180613835021</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9953936483270516E-2</v>
+        <v>1.9775613870160861E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16532,7 +16617,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16565,7 +16650,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-27.17</v>
+        <v>-27.414999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16805,7 +16890,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>27.17</v>
+        <v>27.414999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17403,7 +17488,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>27.17</v>
+        <v>27.414999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17416,7 +17501,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11681748174457507</v>
+        <v>0.11330244753933805</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17542,33 +17627,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>3.8601650015018389</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>23.269525289089753</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>27.12969029059159</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.16438328980676686</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919A13F-E6CB-4C20-9971-AE6D835C6BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6296F37B-CE9A-4CEC-BC17-992F6E6E12F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2391,9 +2391,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>The Kraft Heinz Company</t>
-  </si>
-  <si>
     <t>KHC</t>
   </si>
   <si>
@@ -2413,6 +2410,9 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>The Kraft Heinz</t>
   </si>
 </sst>
 </file>
@@ -3794,29 +3794,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4159,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4206,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" s="49" t="s">
         <v>436</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4228,7 +4228,7 @@
         <v>425</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
@@ -4276,13 +4276,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4306,7 +4306,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4322,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4386,22 +4386,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4439,13 +4439,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4474,13 +4474,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4496,13 +4496,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4566,13 +4566,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4588,7 +4588,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4610,22 +4610,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4686,22 +4686,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4759,22 +4759,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4811,13 +4811,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4830,13 +4830,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4967,13 +4967,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -5012,13 +5012,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5161,13 +5161,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5180,22 +5180,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5528,13 +5528,13 @@
       <c r="F167" s="36"/>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+      <c r="B169" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
+      <c r="C169" s="345"/>
+      <c r="D169" s="345"/>
+      <c r="E169" s="345"/>
+      <c r="F169" s="345"/>
     </row>
     <row r="171" spans="1:6">
       <c r="B171" s="234" t="s">
@@ -5571,13 +5571,13 @@
       </c>
     </row>
     <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+      <c r="B178" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
+      <c r="C178" s="346"/>
+      <c r="D178" s="346"/>
+      <c r="E178" s="346"/>
+      <c r="F178" s="346"/>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="1" t="s">
@@ -5585,22 +5585,22 @@
       </c>
     </row>
     <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+      <c r="B181" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
+      <c r="C181" s="343"/>
+      <c r="D181" s="343"/>
+      <c r="E181" s="343"/>
+      <c r="F181" s="343"/>
     </row>
     <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+      <c r="B182" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
+      <c r="C182" s="343"/>
+      <c r="D182" s="343"/>
+      <c r="E182" s="343"/>
+      <c r="F182" s="343"/>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="1" t="s">
@@ -5624,17 +5624,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5651,6 +5640,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6312,7 +6312,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12074,7 +12074,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="E7" s="353" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz Company(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="353"/>
       <c r="H7" s="276">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6296F37B-CE9A-4CEC-BC17-992F6E6E12F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F076BE22-0815-4E5B-AC02-5D1500BCD006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,18 +2356,69 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
   </si>
   <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
+    <t>The Kraft Heinz</t>
+  </si>
+  <si>
     <t>KHC</t>
   </si>
   <si>
@@ -2410,9 +2438,6 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
-  </si>
-  <si>
-    <t>The Kraft Heinz</t>
   </si>
 </sst>
 </file>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,29 +3803,56 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>442</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>USD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D22" s="32" t="str">
+      <c r="C23" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>438</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (USD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>14.373490987382715</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (USD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>32.464859269378167</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.11330244753933805</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>KHC (USD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>14.373490987382715</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>22.157904669779033</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>29.895007167811503</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>27.12969029059159</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>5023.2701205832382</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>1164</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-1164</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-912</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-912</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-12.097342754012749</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-1068.9302313516419</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-12.097342754012749</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2548</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-1068.9302313516419</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>3030.2425464775833</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2548</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>3030.2425464775833</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>9.2619639153127764E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.8362210468721511E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.739592592287465</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>19869</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>16.649068991502919</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>1334</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-594.28499848473007</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.49797634205986613</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-594.28499848473007</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-0.49797634205986613</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>14.592547258724681</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-26.938493611476797</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>14.592547258724681</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-26.938493611476797</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>62.43 USD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>30</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>43.96 USD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>30</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>30.87 USD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>30</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>21.47 USD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>14.59 USD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>32.464859269378167</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>1.6</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>KHC</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>2.5422740524781333</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>11.831216934904582</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>14.373490987382715</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.55726002481272963</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>3.3703703703703702</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>18.787534299408662</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>22.157904669779033</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.31748034125381119</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>4.1233551795966088</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>25.771651988214895</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>7.9157962159738249E-2</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>3.8601650015018389</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>23.269525289089753</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>27.12969029059159</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.16438328980676686</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="344" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="345"/>
-      <c r="D169" s="345"/>
-      <c r="E169" s="345"/>
-      <c r="F169" s="345"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="346" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="346"/>
-      <c r="D178" s="346"/>
-      <c r="E178" s="346"/>
-      <c r="F178" s="346"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="343" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="343"/>
-      <c r="D181" s="343"/>
-      <c r="E181" s="343"/>
-      <c r="F181" s="343"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="343" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="343"/>
-      <c r="D182" s="343"/>
-      <c r="E182" s="343"/>
-      <c r="F182" s="343"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6182,7 +6299,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>4184</v>
@@ -6218,7 +6335,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-1023</v>
@@ -6254,7 +6371,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-3008</v>
@@ -6312,7 +6429,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7543,7 +7660,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7991,11 +8108,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8025,11 +8142,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8161,15 +8278,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8226,7 +8343,7 @@
       <c r="C4" s="19">
         <v>2147</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8236,7 +8353,7 @@
       <c r="G4" s="19">
         <v>1334</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8247,7 +8364,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8257,7 +8374,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8268,7 +8385,7 @@
       <c r="C6" s="19">
         <v>3376</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8278,7 +8395,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8289,7 +8406,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8299,7 +8416,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8310,7 +8427,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8320,7 +8437,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8331,7 +8448,7 @@
       <c r="C9" s="19">
         <v>215</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8341,7 +8458,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8352,10 +8469,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8364,10 +8481,10 @@
       <c r="C11" s="19">
         <v>583</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8425,7 +8542,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8434,7 +8551,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8445,7 +8562,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8454,7 +8571,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8465,7 +8582,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8474,7 +8591,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8485,7 +8602,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8494,7 +8611,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8505,7 +8622,7 @@
       <c r="C19" s="19">
         <v>7152</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8514,7 +8631,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8525,7 +8642,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8534,7 +8651,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8545,7 +8662,7 @@
       <c r="C21" s="19">
         <v>40099</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8554,7 +8671,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8565,10 +8682,10 @@
       <c r="C22" s="19">
         <v>0</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8578,10 +8695,10 @@
         <f>28673+4708</f>
         <v>33381</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8914,13 +9031,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8936,7 +9053,7 @@
         <f>H29</f>
         <v>-32148.400000000001</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -8951,23 +9068,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-26.938493611476797</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -8981,7 +9098,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.7124439461883409</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -8992,22 +9109,22 @@
         <f>G29/G32</f>
         <v>0.55717149750246353</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9021,7 +9138,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>6.1550492794958195E-2</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9035,22 +9152,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9072,22 +9189,22 @@
         <f>G39/G32</f>
         <v>8.1008529002004823E-2</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9101,7 +9218,7 @@
         <f>G28/G29</f>
         <v>2.7240755422739934E-3</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9120,13 +9237,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9154,7 +9271,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9164,7 +9281,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9174,7 +9291,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9184,26 +9301,26 @@
         <f>SUM(C66:C69)</f>
         <v>1334</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9214,65 +9331,65 @@
         <v>-1928.2849984847301</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>0.71453312200411223</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>0.69180645031635546</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>1928.2849984847301</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9286,7 +9403,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9300,7 +9417,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9314,7 +9431,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9328,11 +9445,11 @@
         <f>SUM(D79:D81)</f>
         <v>0</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9343,15 +9460,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9361,14 +9478,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-16.649068991502919</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9378,13 +9495,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9395,24 +9512,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-20463.284998484731</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>-17.147045333562783</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
@@ -9431,22 +9548,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9533,7 +9650,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9547,7 +9664,7 @@
         <v>26253.25</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9603,7 +9720,7 @@
         <f>C25</f>
         <v>-17575.979879416762</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-16878</v>
@@ -9658,7 +9775,7 @@
         <f>C4+C5</f>
         <v>8677.2701205832382</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>8968</v>
@@ -9713,7 +9830,7 @@
         <f>C35</f>
         <v>-3654</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-3616</v>
@@ -9769,7 +9886,7 @@
         <v>5023.2701205832382</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9825,7 +9942,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>1164</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>1164</v>
@@ -9880,7 +9997,7 @@
         <f>-C4*C78</f>
         <v>-1164</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-1164</v>
@@ -9936,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -9992,7 +10109,7 @@
         <f>C50</f>
         <v>-912</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-912</v>
@@ -10047,7 +10164,7 @@
         <f>SUM(C8:C12)</f>
         <v>4111.2701205832382</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>4440</v>
@@ -10102,7 +10219,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1068.9302313516419</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-1890</v>
@@ -10158,7 +10275,7 @@
         <v>-12.097342754012749</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10215,7 +10332,7 @@
         <v>3030.2425464775833</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10272,8 +10389,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10297,8 +10414,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10323,7 +10440,7 @@
         <v>3030.2425464775833</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10419,7 +10536,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10443,7 +10560,7 @@
         <v>-17575.979879416762</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10500,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10557,7 +10674,7 @@
         <v>-17575.979879416762</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10606,14 +10723,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10625,8 +10742,8 @@
         <v>0.6694782504801029</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10685,8 +10802,8 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10743,7 +10860,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.6694782504801029</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.65302174417704872</v>
@@ -10791,14 +10908,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10809,8 +10926,8 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-3654</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10867,8 +10984,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10926,7 +11043,7 @@
         <v>-3654</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -10975,14 +11092,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -10995,7 +11112,7 @@
         <v>0.13918276784779027</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11053,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11109,7 +11226,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.13918276784779027</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.13990559467615879</v>
@@ -11157,26 +11274,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.26</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11255,7 +11372,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11266,7 +11383,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-912</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-912</v>
@@ -11315,111 +11432,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11433,7 +11550,7 @@
         <f>C47+C48</f>
         <v>-912</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-912</v>
@@ -11481,14 +11598,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11502,8 +11619,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11529,8 +11646,8 @@
         <f>G54</f>
         <v>4.5900649252604557E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11556,7 +11673,7 @@
         <f>-C8/C47</f>
         <v>5.507971623446533</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>5.8684210526315788</v>
@@ -11604,14 +11721,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11625,7 +11742,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11680,7 +11797,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11735,7 +11852,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11790,7 +11907,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11841,11 +11958,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11901,7 +12018,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>196</v>
@@ -11949,14 +12066,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -11970,7 +12087,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -11995,7 +12112,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12020,7 +12137,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12046,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12074,7 +12191,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12096,7 +12213,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12120,7 +12237,7 @@
         <v>0.6694782504801029</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12177,7 +12294,7 @@
         <v>0.3305217495198971</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12234,7 +12351,7 @@
         <v>0.13918276784779027</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12291,7 +12408,7 @@
         <v>0.19133898167210681</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12348,7 +12465,7 @@
         <v>4.4337367754468497E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12405,8 +12522,8 @@
         <v>4.4337367754468497E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>441</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12464,7 +12581,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12521,7 +12638,7 @@
         <v>3.4738556178758817E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12578,7 +12695,7 @@
         <v>0.15660042549334799</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12635,7 +12752,7 @@
         <v>4.0716110628270477E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12688,12 +12805,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>4.6079410183549652E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12750,7 +12867,7 @@
         <v>0.11542352076324201</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12802,26 +12919,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12831,7 +12948,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12857,7 +12974,7 @@
         <v>0.11542352076324201</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12906,14 +13023,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12925,7 +13042,7 @@
         <f>G90</f>
         <v>1.6</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>1.6</v>
@@ -12981,7 +13098,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1909.4401024000001</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1909.4401024000001</v>
@@ -13036,7 +13153,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.63012781093037351</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.74938779529042387</v>
@@ -13085,13 +13202,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>5.8362210468721511E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>5.8362210468721511E-2</v>
@@ -13139,7 +13256,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13148,7 +13265,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13172,7 +13289,7 @@
         <v>1.5756790218989458E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13229,7 +13346,7 @@
         <v>-7.4038261129901306E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13307,7 +13424,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13322,7 +13439,7 @@
         <v>88287</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13379,7 +13496,7 @@
         <v>2147</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13436,7 +13553,7 @@
         <v>3376</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13493,7 +13610,7 @@
         <v>38962</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13550,7 +13667,7 @@
         <v>49325</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13599,7 +13716,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13608,7 +13725,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13634,7 +13751,7 @@
         <v>8.1780351004161395E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13691,7 +13808,7 @@
         <v>0.12859360269680897</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13748,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13767,63 +13884,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.5236707938820102</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.3970484891075192</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.042652027027027</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.23828125</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>13.653739612188366</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.8375581996896015</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>-0.2510239906377999</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>4.7952684258416742E-2</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4382207578253707</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8129829984544048</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13831,58 +13948,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.642072213500785</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6769295655841416</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.2506836827711942</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-26.954773869346734</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>-5.8331360946745558</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.620795107033639</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>-0.24662259269905146</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.7913446676970631E-2</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4481614597732928</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.6272630457933972</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13891,7 +14008,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -13947,7 +14064,7 @@
         <f>C81</f>
         <v>0.15660042549334799</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.17178673682581444</v>
@@ -14001,7 +14118,7 @@
         <f>C4/C101</f>
         <v>0.29736257886212014</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.29274978196110413</v>
@@ -14056,7 +14173,7 @@
         <v>1.7899036999493159</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14113,7 +14230,7 @@
         <v>0.10184024572900635</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14209,7 +14326,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14234,7 +14351,7 @@
         <v>2.5391674073829975</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14291,7 +14408,7 @@
         <v>9.2619639153127764E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14340,7 +14457,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15091,13 +15208,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15141,7 +15258,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15151,7 +15268,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15169,10 +15286,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15187,8 +15304,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15203,8 +15320,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15219,8 +15336,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15284,7 +15401,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15294,7 +15411,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15304,7 +15421,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16565,7 +16682,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16618,12 +16735,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16636,19 +16753,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-27.414999999999999</v>
       </c>
@@ -16665,19 +16782,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.6</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
@@ -16691,13 +16808,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>34.064859269378168</v>
       </c>
@@ -16714,15 +16831,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16739,12 +16856,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16761,37 +16878,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16805,12 +16922,12 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16823,12 +16940,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16841,8 +16958,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16858,7 +16975,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16868,25 +16985,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16896,12 +17013,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16911,8 +17028,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16932,8 +17049,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16943,8 +17060,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16958,8 +17075,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16969,8 +17086,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16990,8 +17107,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17001,8 +17118,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17016,8 +17133,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17027,8 +17144,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17048,8 +17165,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17059,8 +17176,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17074,8 +17191,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17086,8 +17203,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17149,8 +17266,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17160,8 +17277,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17175,8 +17292,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17186,12 +17303,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17207,8 +17324,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17218,8 +17335,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17233,8 +17350,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17244,8 +17361,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17260,16 +17377,16 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17278,10 +17395,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17293,8 +17410,8 @@
         <v>30</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17305,8 +17422,8 @@
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17321,23 +17438,23 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17345,38 +17462,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>-0.52817248309270792</v>
       </c>
@@ -17396,10 +17513,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17420,15 +17537,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17469,7 +17586,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.55726002481272963</v>
       </c>
@@ -17479,14 +17596,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>27.414999999999999</v>
       </c>
@@ -17497,9 +17614,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.11330244753933805</v>
       </c>
@@ -17509,15 +17626,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17558,28 +17675,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.31748034125381119</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17591,7 +17708,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17603,23 +17720,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>29.895007167811503</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>7.9157962159738249E-2</v>
       </c>
@@ -17629,15 +17746,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17663,19 +17780,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>27.12969029059159</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.16438328980676686</v>
       </c>
@@ -17684,33 +17801,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F076BE22-0815-4E5B-AC02-5D1500BCD006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF10580-2CA6-4008-A5E5-F6406046BF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4254,7 +4254,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>27.414999999999999</v>
+        <v>27.74</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>32717.062754559996</v>
+        <v>33104.917775359994</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11330244753933805</v>
+        <v>0.10870597389897529</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>22.157904669779033</v>
+        <v>21.274057798092517</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.2619639153127764E-2</v>
+        <v>9.1534513604289755E-2</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8362210468721511E-2</v>
+        <v>5.7678442682047588E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>3.3703703703703702</v>
+        <v>3.2806413181838994</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>18.787534299408662</v>
+        <v>17.993416479908618</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>22.157904669779033</v>
+        <v>21.274057798092517</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31748034125381119</v>
+        <v>0.34470506643597709</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8362210468721511E-2</v>
+        <v>5.7678442682047588E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8362210468721511E-2</v>
+        <v>5.7678442682047588E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14405,50 +14405,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.2619639153127764E-2</v>
+        <v>9.1534513604289755E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.7879851841066272E-2</v>
+        <v>7.6967416662683197E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.2469830735937255E-2</v>
+        <v>7.1620779005974036E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3529904815404118E-2</v>
+        <v>3.3137070674632438E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-6.082453106896462E-3</v>
+        <v>-6.0111914897464499E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.5827501886067895E-2</v>
+        <v>-2.5524908587114325E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.99843542606303E-2</v>
+        <v>2.9633059554981241E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.31900785465667525</v>
+        <v>-0.31527037979137534</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.33618543579273463</v>
+        <v>0.33224670952623725</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11055393410876636</v>
+        <v>0.10925869154981362</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.8700620439074263E-2</v>
+        <v>2.8364365873728224E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14462,43 +14462,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3931739856973303E-2</v>
+        <v>8.294840116001885E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6988248955916239E-2</v>
+        <v>8.5969100401097467E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2378135462968965E-2</v>
+        <v>7.1530158028741672E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1298653173175768E-2</v>
+        <v>3.0931960228645049E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1033997847184035E-2</v>
+        <v>1.0904724260293812E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9082320882567145E-2</v>
+        <v>5.8390116330049688E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31341444300560967</v>
+        <v>-0.3097425001802015</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.33591034997382979</v>
+        <v>0.33197484659454013</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1113180613835021</v>
+        <v>0.11001386636008327</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9775613870160861E-2</v>
+        <v>1.9543924089778661E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="I3" s="262">
         <f>-Market_Price</f>
-        <v>-27.414999999999999</v>
+        <v>-27.74</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>27.414999999999999</v>
+        <v>27.74</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="C86" s="264">
         <f>Market_Price</f>
-        <v>27.414999999999999</v>
+        <v>27.74</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11330244753933805</v>
+        <v>0.10870597389897529</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.3703703703703702</v>
+        <v>3.2806413181838994</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>18.787534299408662</v>
+        <v>17.993416479908618</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>22.157904669779033</v>
+        <v>21.274057798092517</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.31748034125381119</v>
+        <v>0.34470506643597709</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF10580-2CA6-4008-A5E5-F6406046BF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3C88E5-CEB4-4C3A-9B79-CDC5747316D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>32.464859269378167</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.10870597389897529</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>KHC (USD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>14.373490987382715</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>21.274057798092517</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>27.12969029059159</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-912</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>14.373490987382715</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>21.274057798092517</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>27.12969029059159</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8108,11 +8114,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8142,11 +8148,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9368,7 +9374,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -11439,104 +11445,104 @@
         <v>0</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13900,47 +13906,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.5236707938820102</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.3970484891075192</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.042652027027027</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.23828125</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>13.653739612188366</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.8375581996896015</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>-0.2510239906377999</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>4.7952684258416742E-2</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4382207578253707</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8129829984544048</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13952,47 +13958,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.642072213500785</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6769295655841416</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.2506836827711942</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-26.954773869346734</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>-5.8331360946745558</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.620795107033639</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>-0.24662259269905146</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.7913446676970631E-2</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4481614597732928</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.6272630457933972</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15286,10 +15292,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15304,8 +15310,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15320,8 +15326,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15336,8 +15342,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16831,11 +16837,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16856,8 +16862,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16878,8 +16884,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16889,8 +16895,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16903,8 +16909,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16922,8 +16928,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16940,8 +16946,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -16958,8 +16964,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16985,21 +16991,21 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17013,8 +17019,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17028,8 +17034,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17049,8 +17055,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17060,8 +17066,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17075,8 +17081,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17086,8 +17092,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17107,8 +17113,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17118,8 +17124,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17133,8 +17139,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17144,8 +17150,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17165,8 +17171,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17176,8 +17182,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17191,8 +17197,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17203,8 +17209,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17266,8 +17272,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17277,8 +17283,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17292,8 +17298,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17303,8 +17309,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17324,8 +17330,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17335,8 +17341,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17350,8 +17356,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17361,8 +17367,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17379,7 +17385,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17493,7 +17499,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-0.52817248309270792</v>
       </c>
@@ -17586,7 +17592,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.55726002481272963</v>
       </c>
@@ -17675,7 +17681,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.34470506643597709</v>
       </c>
@@ -17685,7 +17691,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17696,7 +17702,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17708,7 +17714,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17720,7 +17726,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17736,7 +17742,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>7.9157962159738249E-2</v>
       </c>
@@ -17792,7 +17798,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.16438328980676686</v>
       </c>
@@ -17801,32 +17807,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3C88E5-CEB4-4C3A-9B79-CDC5747316D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82547FE0-9EB2-4A67-B15E-F9BCFB77DB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.739592592287465</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>19869</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>-594.28499848473007</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>0</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>14.592547258724681</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.08</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>30</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>62.43 USD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.06</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>30</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>43.96 USD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.04</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>30</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>30.87 USD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>30</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>21.47 USD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>30</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>14.59 USD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-19869</v>
       </c>
       <c r="D86" s="248">
@@ -9494,7 +9494,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>-594.28499848473007</v>
       </c>
       <c r="D87" s="248">
@@ -9511,7 +9511,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>0</v>
       </c>
       <c r="D88" s="248">
@@ -15471,7 +15471,7 @@
         <v>3160.0180167683388</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15493,7 +15493,7 @@
         <v>3295.3513499795931</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15515,7 +15515,7 @@
         <v>3436.4805713727765</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15537,7 +15537,7 @@
         <v>3583.6539000600628</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15559,7 +15559,7 @@
         <v>3737.1301855739739</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15581,7 +15581,7 @@
         <v>3897.1793631338364</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15603,7 +15603,7 @@
         <v>4064.0829284098313</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15625,7 +15625,7 @@
         <v>4238.1344326196504</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15647,7 +15647,7 @@
         <v>4419.639998828533</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15669,7 +15669,7 @@
         <v>4608.9188603607645</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15691,7 +15691,7 @@
         <v>4806.3039222695952</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E31" s="125">
@@ -15713,7 +15713,7 @@
         <v>5012.1423468530957</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E32" s="125">
@@ -15735,7 +15735,7 @@
         <v>5226.7961642457558</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E33" s="125">
@@ -15757,7 +15757,7 @@
         <v>5450.6429091597538</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E34" s="125">
@@ -15779,7 +15779,7 @@
         <v>5684.0762848957738</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E35" s="125">
@@ -15801,7 +15801,7 @@
         <v>5927.5068557912755</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E36" s="125">
@@ -15823,7 +15823,7 @@
         <v>6181.3627693240651</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E37" s="125">
@@ -15845,7 +15845,7 @@
         <v>6446.0905091412214</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E38" s="125">
@@ -15867,7 +15867,7 @@
         <v>6722.1556803378289</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E39" s="125">
@@ -15889,7 +15889,7 @@
         <v>7010.0438283666326</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E40" s="125">
@@ -15911,7 +15911,7 @@
         <v>7310.2612930189507</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E41" s="125">
@@ -15933,7 +15933,7 @@
         <v>7623.3360989788298</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E42" s="125">
@@ -15955,7 +15955,7 @@
         <v>7949.8188845167324</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E43" s="125">
@@ -15977,7 +15977,7 @@
         <v>8290.2838699561817</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E44" s="125">
@@ -15999,7 +15999,7 @@
         <v>8645.3298676166814</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E45" s="125">
@@ -16021,7 +16021,7 @@
         <v>9015.581335009234</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E46" s="125">
@@ -16043,7 +16043,7 @@
         <v>9401.6894731367938</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E47" s="125">
@@ -16065,7 +16065,7 @@
         <v>9804.3333718313897</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E48" s="125">
@@ -16087,7 +16087,7 @@
         <v>10224.221204142301</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E49" s="125">
@@ -16109,7 +16109,7 @@
         <v>10662.091471876032</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="E50" s="125">
@@ -16810,7 +16810,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17027,7 +17027,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>14.592547258724681</v>
       </c>
       <c r="D22" t="str">
@@ -17074,7 +17074,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>30.872623002991254</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17132,7 +17132,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>21.465870772746047</v>
       </c>
       <c r="D33" t="str">
@@ -17190,7 +17190,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>43.960023112166873</v>
       </c>
       <c r="D39" t="str">
@@ -17291,7 +17291,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>14.592547258724657</v>
       </c>
       <c r="D51" t="str">
@@ -17349,7 +17349,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>62.434508619809236</v>
       </c>
       <c r="D57" t="str">
@@ -17437,7 +17437,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>32.46666798264237</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82547FE0-9EB2-4A67-B15E-F9BCFB77DB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DDBBC8-BBB3-4B7D-9DCD-AF57D280474A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DDBBC8-BBB3-4B7D-9DCD-AF57D280474A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17824CC8-A5E3-4F58-8F07-9B05BC637D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,28 +2402,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>The Kraft Heinz</t>
+  </si>
+  <si>
+    <t>KHC</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>CNS_01</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>The Kraft Heinz</t>
-  </si>
-  <si>
-    <t>KHC</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>CNS_01</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>444</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>444</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>32.464859269378167</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.10870597389897529</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>KHC (USD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>14.373490987382715</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>21.274057798092517</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>27.12969029059159</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-912</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>9.1534513604289755E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.7678442682047588E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.63012781093037351</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.739592592287465</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>16.649068991502919</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.78990369994931575</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.40281804358844397</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>3.955391512509995</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>14.592547258724681</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-26.938493611476797</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>30</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>62.43 USD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>30</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>43.96 USD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>30</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>30.87 USD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>30</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>21.47 USD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>30</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>14.59 USD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>KHC</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>14.373490987382715</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>21.274057798092517</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>29.895007167811503</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>27.12969029059159</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6305,7 +6361,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>4184</v>
@@ -6341,7 +6397,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-1023</v>
@@ -6377,7 +6433,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-3008</v>
@@ -6435,7 +6491,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7666,7 +7722,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8114,11 +8170,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8148,11 +8204,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8255,17 +8311,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8349,7 +8405,7 @@
       <c r="C4" s="19">
         <v>2147</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8359,7 +8415,7 @@
       <c r="G4" s="19">
         <v>1334</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8370,7 +8426,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8380,7 +8436,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8391,7 +8447,7 @@
       <c r="C6" s="19">
         <v>3376</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8401,7 +8457,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8412,7 +8468,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8422,7 +8478,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8433,7 +8489,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8443,7 +8499,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8454,7 +8510,7 @@
       <c r="C9" s="19">
         <v>215</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8464,7 +8520,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8475,10 +8531,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8487,10 +8543,10 @@
       <c r="C11" s="19">
         <v>583</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8548,7 +8604,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8557,7 +8613,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8568,7 +8624,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8577,7 +8633,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8588,7 +8644,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8597,7 +8653,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8608,7 +8664,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8617,7 +8673,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8628,7 +8684,7 @@
       <c r="C19" s="19">
         <v>7152</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8637,7 +8693,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8648,7 +8704,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8657,7 +8713,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8668,7 +8724,7 @@
       <c r="C21" s="19">
         <v>40099</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8677,7 +8733,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8688,10 +8744,10 @@
       <c r="C22" s="19">
         <v>0</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8701,10 +8757,10 @@
         <f>28673+4708</f>
         <v>33381</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9037,13 +9093,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9059,7 +9115,7 @@
         <f>H29</f>
         <v>-32148.400000000001</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9074,23 +9130,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-26.938493611476797</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9104,7 +9160,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.7124439461883409</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9115,22 +9171,22 @@
         <f>G29/G32</f>
         <v>0.55717149750246353</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9144,7 +9200,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>6.1550492794958195E-2</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9158,22 +9214,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9195,22 +9251,22 @@
         <f>G39/G32</f>
         <v>8.1008529002004823E-2</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9224,7 +9280,7 @@
         <f>G28/G29</f>
         <v>2.7240755422739934E-3</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9243,13 +9299,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9277,7 +9333,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9287,7 +9343,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9297,7 +9353,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9307,26 +9363,26 @@
         <f>SUM(C66:C69)</f>
         <v>1334</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9337,65 +9393,65 @@
         <v>-1928.2849984847301</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>0.71453312200411223</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>0.69180645031635546</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>1928.2849984847301</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9409,7 +9465,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9423,7 +9479,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9437,7 +9493,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9451,11 +9507,11 @@
         <f>SUM(D79:D81)</f>
         <v>0</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9466,76 +9522,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-19869</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-16.649068991502919</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>-594.28499848473007</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-0.49797634205986613</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>0</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-20463.284998484731</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-17.147045333562783</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
@@ -9656,7 +9712,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9670,7 +9726,7 @@
         <v>26253.25</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9726,7 +9782,7 @@
         <f>C25</f>
         <v>-17575.979879416762</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-16878</v>
@@ -9781,7 +9837,7 @@
         <f>C4+C5</f>
         <v>8677.2701205832382</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>8968</v>
@@ -9836,7 +9892,7 @@
         <f>C35</f>
         <v>-3654</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-3616</v>
@@ -9892,7 +9948,7 @@
         <v>5023.2701205832382</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9948,7 +10004,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>1164</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>1164</v>
@@ -10003,7 +10059,7 @@
         <f>-C4*C78</f>
         <v>-1164</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-1164</v>
@@ -10059,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10115,7 +10171,7 @@
         <f>C50</f>
         <v>-912</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-912</v>
@@ -10170,7 +10226,7 @@
         <f>SUM(C8:C12)</f>
         <v>4111.2701205832382</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>4440</v>
@@ -10225,7 +10281,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1068.9302313516419</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-1890</v>
@@ -10281,7 +10337,7 @@
         <v>-12.097342754012749</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10338,7 +10394,7 @@
         <v>3030.2425464775833</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10395,8 +10451,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10420,8 +10476,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10446,7 +10502,7 @@
         <v>3030.2425464775833</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10542,7 +10598,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10566,7 +10622,7 @@
         <v>-17575.979879416762</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10623,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10680,7 +10736,7 @@
         <v>-17575.979879416762</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10729,14 +10785,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10748,8 +10804,8 @@
         <v>0.6694782504801029</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10808,8 +10864,8 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10866,7 +10922,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.6694782504801029</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.65302174417704872</v>
@@ -10914,14 +10970,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10932,8 +10988,8 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-3654</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10990,8 +11046,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11049,7 +11105,7 @@
         <v>-3654</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11098,14 +11154,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11118,7 +11174,7 @@
         <v>0.13918276784779027</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11176,7 +11232,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11232,7 +11288,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.13918276784779027</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.13990559467615879</v>
@@ -11280,26 +11336,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.26</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11378,7 +11434,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11389,7 +11445,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-912</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-912</v>
@@ -11438,111 +11494,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11556,7 +11612,7 @@
         <f>C47+C48</f>
         <v>-912</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-912</v>
@@ -11604,14 +11660,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11625,8 +11681,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11652,8 +11708,8 @@
         <f>G54</f>
         <v>4.5900649252604557E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11679,7 +11735,7 @@
         <f>-C8/C47</f>
         <v>5.507971623446533</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>5.8684210526315788</v>
@@ -11727,14 +11783,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11748,7 +11804,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11803,7 +11859,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11858,7 +11914,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11913,7 +11969,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11964,11 +12020,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12024,7 +12080,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>196</v>
@@ -12072,14 +12128,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12093,7 +12149,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12118,7 +12174,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12143,7 +12199,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12169,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12197,7 +12253,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12219,7 +12275,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12243,7 +12299,7 @@
         <v>0.6694782504801029</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12300,7 +12356,7 @@
         <v>0.3305217495198971</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12357,7 +12413,7 @@
         <v>0.13918276784779027</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12414,7 +12470,7 @@
         <v>0.19133898167210681</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12471,7 +12527,7 @@
         <v>4.4337367754468497E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12528,8 +12584,8 @@
         <v>4.4337367754468497E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12587,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12644,7 +12700,7 @@
         <v>3.4738556178758817E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12701,7 +12757,7 @@
         <v>0.15660042549334799</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12758,7 +12814,7 @@
         <v>4.0716110628270477E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12811,12 +12867,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>4.6079410183549652E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12873,7 +12929,7 @@
         <v>0.11542352076324201</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12925,26 +12981,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12954,7 +13010,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12980,7 +13036,7 @@
         <v>0.11542352076324201</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13029,14 +13085,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13048,7 +13104,7 @@
         <f>G90</f>
         <v>1.6</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>1.6</v>
@@ -13104,7 +13160,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1909.4401024000001</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1909.4401024000001</v>
@@ -13159,7 +13215,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.63012781093037351</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.74938779529042387</v>
@@ -13208,13 +13264,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>5.7678442682047588E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>5.7678442682047588E-2</v>
@@ -13262,7 +13318,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13271,7 +13327,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13295,7 +13351,7 @@
         <v>1.5756790218989458E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13352,7 +13408,7 @@
         <v>-7.4038261129901306E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13430,7 +13486,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13445,7 +13501,7 @@
         <v>88287</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13502,7 +13558,7 @@
         <v>2147</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13559,7 +13615,7 @@
         <v>3376</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13616,7 +13672,7 @@
         <v>38962</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13673,7 +13729,7 @@
         <v>49325</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13722,7 +13778,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13731,7 +13787,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13757,7 +13813,7 @@
         <v>8.1780351004161395E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13814,7 +13870,7 @@
         <v>0.12859360269680897</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13871,7 +13927,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13890,63 +13946,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.5236707938820102</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.3970484891075192</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.042652027027027</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.23828125</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>13.653739612188366</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.8375581996896015</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>-0.2510239906377999</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>4.7952684258416742E-2</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4382207578253707</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8129829984544048</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13954,58 +14010,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.642072213500785</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6769295655841416</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.2506836827711942</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-26.954773869346734</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>-5.8331360946745558</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.620795107033639</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>-0.24662259269905146</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.7913446676970631E-2</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4481614597732928</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.6272630457933972</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14014,7 +14070,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14070,7 +14126,7 @@
         <f>C81</f>
         <v>0.15660042549334799</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.17178673682581444</v>
@@ -14124,7 +14180,7 @@
         <f>C4/C101</f>
         <v>0.29736257886212014</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.29274978196110413</v>
@@ -14179,7 +14235,7 @@
         <v>1.7899036999493159</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14236,7 +14292,7 @@
         <v>0.10184024572900635</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14332,7 +14388,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14357,7 +14413,7 @@
         <v>2.5391674073829975</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14414,7 +14470,7 @@
         <v>9.1534513604289755E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14463,7 +14519,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15196,7 +15252,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15264,7 +15320,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15274,7 +15330,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15292,10 +15348,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15310,8 +15366,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15326,8 +15382,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15342,8 +15398,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16688,7 +16744,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16719,12 +16775,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16739,6 +16795,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>1909.4401024000001</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>23868.00128</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>20</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>30</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>31.262980564067469</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>1991.2152354067734</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>1843.717810561827</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>2076.4925324090918</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>1780.257658101073</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>2165.4219797438864</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>1718.9817829344215</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>2258.1599871769426</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>1659.8150029655089</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>2354.8696629975484</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>1602.6847238406681</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>2455.7211008945515</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>1547.5208498796862</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>2560.8916791183888</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>1494.2556980722984</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>2670.5663724552605</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>1442.8239150348916</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>2784.9380775621421</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>1393.1623968255328</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>2904.2079522348399</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>1345.2102115189336</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>3028.585769205808</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0.42888285933767062</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>1298.9085244463656</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>3158.2902850939654</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0.39711375864599124</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>1254.2005260087838</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>3293.5496251554509</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0.36769792467221413</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>1211.031361974608</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>3434.601684511998</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0.34046104136316119</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>1169.3480661766225</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>3581.6945465626236</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0.31524170496588994</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>1129.0994955254316</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>3735.0869193145372</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0.29189046756100923</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>1090.2362672597299</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>3895.0485904006841</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0.27026895144537894</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>1052.7106983563942</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>4061.8609015842144</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0.25024902911609154</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>1016.4767470260618</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>4235.8172435844508</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0.23171206399638106</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>981.48995622241466</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>4417.223572094641</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0.21454820740405653</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>947.70739909584847</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>4606.3989458990727</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0.19865574759634863</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>915.08762632461253</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>4803.6760880360225</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0.18394050703365611</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>883.59061525879565</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>5009.4019709934719</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0.17031528429042234</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>853.17772081475516</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>5223.9384269668726</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0.1576993373059466</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>823.81162805974486</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>5447.6627842522748</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0.1460179049129135</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>795.45630642856622</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>5680.9685308941016</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0.13520176380825324</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>768.07696551606375</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>5924.266006754824</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0.12518681834097523</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>741.64001239123081</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>6177.9831252237209</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0.11591372068608817</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>716.11301038054842</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>6442.5661258340942</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0.10732751915378534</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>691.4646392699874</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>6718.4803591126474</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>4.2826760003620602E-2</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>9.9377332549801231E-2</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>667.66465687684558</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>24890.190442584666</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>9.9377332549801231E-2</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>2473.5207328406204</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>37309.243005988872</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>37309.243005988872</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.08</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>23868.001279999997</v>
+      </c>
+      <c r="C51" s="124">
+        <v>24638.107943878487</v>
+      </c>
+      <c r="D51" s="124">
+        <v>25431.278966279071</v>
+      </c>
+      <c r="E51" s="124">
+        <v>26248.526485762472</v>
+      </c>
+      <c r="F51" s="124">
+        <v>27090.893979383956</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>23868.001279999993</v>
+      </c>
+      <c r="C52" s="124">
+        <v>25408.923754298376</v>
+      </c>
+      <c r="D52" s="124">
+        <v>27104.288382592465</v>
+      </c>
+      <c r="E52" s="124">
+        <v>28972.578506455287</v>
+      </c>
+      <c r="F52" s="124">
+        <v>31034.34401181234</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>23868.001279999989</v>
+      </c>
+      <c r="C53" s="124">
+        <v>26363.022046889637</v>
+      </c>
+      <c r="D53" s="124">
+        <v>29285.268319680996</v>
+      </c>
+      <c r="E53" s="124">
+        <v>32719.617157958135</v>
+      </c>
+      <c r="F53" s="124">
+        <v>36767.726107046059</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>23868.001279999989</v>
+      </c>
+      <c r="C54" s="124">
+        <v>27335.095200640651</v>
+      </c>
+      <c r="D54" s="124">
+        <v>31632.71385125567</v>
+      </c>
+      <c r="E54" s="124">
+        <v>36993.969761567991</v>
+      </c>
+      <c r="F54" s="124">
+        <v>43719.305888057068</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>23868.001279999986</v>
+      </c>
+      <c r="C55" s="124">
+        <v>28239.177173977743</v>
+      </c>
+      <c r="D55" s="124">
+        <v>33945.027558267066</v>
+      </c>
+      <c r="E55" s="124">
+        <v>41473.361328896732</v>
+      </c>
+      <c r="F55" s="124">
+        <v>51499.970544673502</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>23868.001279999989</v>
+      </c>
+      <c r="C56" s="124">
+        <v>29036.703239658433</v>
+      </c>
+      <c r="D56" s="124">
+        <v>36110.529837126858</v>
+      </c>
+      <c r="E56" s="124">
+        <v>45952.183653237284</v>
+      </c>
+      <c r="F56" s="124">
+        <v>59844.896436541792</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.04</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.06</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.08</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>20</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>20</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>20</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>20</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>20</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>20</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>20.645304694636323</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>21.309935983277331</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>21.994741979301981</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>22.700597055929062</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>19.999999999999996</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>21.291203612922192</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>22.711820788533547</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>24.277339494474241</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>26.004979342629181</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>19.999999999999993</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>22.090682615289047</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>24.539355412403427</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>27.417140441814269</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>30.809220827263218</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>19.999999999999993</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>22.905223508217151</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>26.506378544366886</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>30.9987998807146</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>36.634241279927629</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>19.999999999999989</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>23.662791737522266</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>28.443963246064538</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>34.752270072692681</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>43.153986746118946</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>19.999999999999993</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>24.331072299706555</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>30.258528490515364</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>38.505263272080136</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>50.14655038307572</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.08</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>30</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>50.14655038307572</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>30</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>38.505263272080136</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>30</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>30.258528490515364</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>30</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>24.331072299706555</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>30</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>19.999999999999993</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16759,19 +18266,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-27.74</v>
       </c>
@@ -16788,19 +18295,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.6</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
@@ -16814,13 +18321,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>34.064859269378168</v>
       </c>
@@ -16837,15 +18344,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16862,12 +18369,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16884,37 +18391,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>448</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16928,12 +18435,12 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16946,12 +18453,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16964,8 +18471,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16981,7 +18488,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16991,25 +18498,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17019,23 +18526,23 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>14.592547258724681</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17055,8 +18562,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17066,23 +18573,23 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>30.872623002991254</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17092,8 +18599,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17113,8 +18620,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17124,23 +18631,23 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>21.465870772746047</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17150,8 +18657,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17171,8 +18678,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17182,23 +18689,23 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>43.960023112166873</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17209,8 +18716,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17272,8 +18779,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17283,23 +18790,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>14.592547258724657</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17309,12 +18816,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17330,8 +18837,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17341,23 +18848,23 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>62.434508619809236</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17367,8 +18874,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17383,16 +18890,16 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17401,10 +18908,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17416,8 +18923,8 @@
         <v>30</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17428,8 +18935,8 @@
         <v>4.2826760003620602E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17437,30 +18944,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>32.46666798264237</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17468,38 +18975,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>-0.52817248309270792</v>
       </c>
@@ -17519,10 +19026,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17543,12 +19050,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17592,7 +19099,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.55726002481272963</v>
       </c>
@@ -17602,14 +19109,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>27.74</v>
       </c>
@@ -17620,9 +19127,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.10870597389897529</v>
       </c>
@@ -17632,12 +19139,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17681,28 +19188,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.34470506643597709</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17714,7 +19221,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17726,23 +19233,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>29.895007167811503</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>7.9157962159738249E-2</v>
       </c>
@@ -17752,12 +19259,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17786,19 +19293,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>27.12969029059159</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.16438328980676686</v>
       </c>
@@ -17807,33 +19314,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CE4DE1-FD71-B042-AF90-B56B4FD37A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A627D6-45FE-1947-AAA2-098685F8549D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="5040" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45754</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15361,10 +15361,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15379,8 +15379,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15395,8 +15395,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15411,8 +15411,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16891,8 +16891,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18357,11 +18357,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18382,8 +18382,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18404,8 +18404,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18415,8 +18415,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18429,8 +18429,8 @@
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18448,8 +18448,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18466,8 +18466,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18484,8 +18484,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18511,21 +18511,21 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18539,8 +18539,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18554,8 +18554,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18575,8 +18575,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18586,8 +18586,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18601,8 +18601,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18612,8 +18612,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18633,8 +18633,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18644,8 +18644,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18659,8 +18659,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18670,8 +18670,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18691,8 +18691,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18702,8 +18702,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18717,8 +18717,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18729,8 +18729,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18792,8 +18792,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18803,8 +18803,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18818,8 +18818,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18829,8 +18829,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18850,8 +18850,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18861,8 +18861,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18876,8 +18876,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18887,8 +18887,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A627D6-45FE-1947-AAA2-098685F8549D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287A7226-FEC4-43EA-A075-C6964AF8AD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="5040" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>416</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>418</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>417</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>420</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>435</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>436</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>32.464859269378167</v>
+        <v>36.134621832566509</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10870597389897529</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.14522234161809888</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>434</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>14.373490987382715</v>
+        <v>16.7846939344021</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>425</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>21.274057798092517</v>
+        <v>23.307997499907511</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4528,13 +4517,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>29.895007167811503</v>
+        <v>33.247786953152008</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>437</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>27.12969029059159</v>
+        <v>29.760030747653474</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4566,11 +4555,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0.63012781093037351</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>431</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>31.739592592287465</v>
+        <v>33.8555654317733</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>0.78990369994931575</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>0.40281804358844397</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>3.955391512509995</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>450</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>62.43 USD</v>
+        <v>68.95 USD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>43.96 USD</v>
+        <v>48.67 USD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>30.87 USD</v>
+        <v>34.37 USD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>21.47 USD</v>
+        <v>24.14 USD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5329,27 +5318,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>14.59 USD</v>
+        <v>16.71 USD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>32.464859269378167</v>
+        <v>36.134621832566509</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,49 +5424,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>2.5422740524781333</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.6516149109837741</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>11.831216934904582</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>14.133079023418324</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>14.373490987382715</v>
+        <v>16.7846939344021</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>417</v>
       </c>
@@ -5490,21 +5479,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55726002481272963</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.53549551418648556</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5513,7 +5502,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5523,30 +5512,30 @@
         <v>3.2806413181838994</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>17.993416479908618</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>20.027356181723611</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>21.274057798092517</v>
+        <v>23.307997499907511</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>417</v>
       </c>
@@ -5559,63 +5548,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34470506643597709</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.35496772021283307</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>4.1233551795966088</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>4.1608411837951351</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>25.771651988214895</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>29.086945769356873</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>29.895007167811503</v>
+        <v>33.247786953152008</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>417</v>
       </c>
@@ -5628,21 +5617,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.9157962159738249E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.9891105344645608E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>424</v>
       </c>
@@ -5651,7 +5640,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5661,30 +5650,30 @@
         <v>3.8601650015018389</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>23.269525289089753</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>25.899865746151637</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>27.12969029059159</v>
+        <v>29.760030747653474</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>417</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16438328980676686</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.17586774670093841</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>USD</v>
@@ -5924,7 +5913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5984,7 +5973,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6009,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6056,7 +6045,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6072,7 +6061,7 @@
       <c r="L7" s="188"/>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6088,7 +6077,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6104,7 +6093,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6120,7 +6109,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6136,7 +6125,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6172,7 +6161,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6188,7 +6177,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6224,7 +6213,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6260,7 +6249,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6296,13 +6285,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6320,7 +6309,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6346,7 +6335,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6372,7 +6361,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6408,7 +6397,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6444,7 +6433,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6480,7 +6469,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (USD)</v>
@@ -6499,7 +6488,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6507,7 +6496,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6534,7 +6523,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6561,7 +6550,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6580,7 +6569,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6599,7 +6588,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6618,7 +6607,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6634,12 +6623,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6688,7 +6677,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6737,7 +6726,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6786,7 +6775,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6835,7 +6824,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6884,7 +6873,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6933,7 +6922,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6982,7 +6971,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7031,7 +7020,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7080,7 +7069,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7129,7 +7118,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7178,7 +7167,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7227,7 +7216,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7276,12 +7265,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7330,7 +7319,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7379,12 +7368,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7433,7 +7422,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7482,7 +7471,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7531,7 +7520,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7580,13 +7569,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7635,7 +7624,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7684,7 +7673,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7733,7 +7722,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7782,7 +7771,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7831,12 +7820,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7886,7 +7875,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7935,7 +7924,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7985,7 +7974,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8034,7 +8023,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8084,7 +8073,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8100,13 +8089,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8155,7 +8144,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8189,7 +8178,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8223,7 +8212,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8272,7 +8261,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8353,7 +8342,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8364,7 +8353,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8380,7 +8369,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8391,7 +8380,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8411,7 +8400,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8432,7 +8421,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8453,7 +8442,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8474,7 +8463,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,7 +8484,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8516,7 +8505,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8537,7 +8526,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8549,7 +8538,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8561,7 +8550,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8585,12 +8574,12 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8610,7 +8599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8630,7 +8619,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8650,7 +8639,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8670,7 +8659,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8690,7 +8679,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8710,7 +8699,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8730,7 +8719,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8750,7 +8739,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8762,7 +8751,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8775,7 +8764,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8799,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8816,7 +8805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8835,7 +8824,7 @@
         <v>-32014.400000000001</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8850,7 +8839,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8869,7 +8858,7 @@
         <v>-32148.400000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8885,7 +8874,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8902,7 +8891,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8922,7 +8911,7 @@
         <v>6947.6</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8933,7 +8922,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -8946,7 +8935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -8965,7 +8954,7 @@
         <v>5747</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8981,7 +8970,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8997,7 +8986,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9013,7 +9002,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9032,7 +9021,7 @@
         <v>715.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9052,7 +9041,7 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9072,7 +9061,7 @@
         <v>1200.6000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9091,7 +9080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9102,7 +9091,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9116,7 +9105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9130,7 +9119,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (USD)</v>
@@ -9145,10 +9134,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9161,7 +9150,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9175,7 +9164,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9186,10 +9175,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9201,7 +9190,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9215,7 +9204,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9229,10 +9218,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9244,7 +9233,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9255,7 +9244,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9266,10 +9255,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9281,7 +9270,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9297,7 +9286,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9308,7 +9297,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9322,7 +9311,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9338,7 +9327,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9348,7 +9337,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9358,7 +9347,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9368,7 +9357,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9378,10 +9367,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9393,7 +9382,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9409,7 +9398,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9425,7 +9414,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9438,7 +9427,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9451,10 +9440,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9466,7 +9455,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9480,7 +9469,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9494,7 +9483,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9508,7 +9497,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9522,7 +9511,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9533,7 +9522,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9541,7 +9530,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9558,7 +9547,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9575,7 +9564,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9592,7 +9581,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9623,19 +9612,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9692,7 +9681,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9715,7 +9704,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9729,7 +9718,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9786,7 +9775,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9841,7 +9830,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9896,7 +9885,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -9951,7 +9940,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10008,7 +9997,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10063,7 +10052,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10118,7 +10107,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10175,7 +10164,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10230,7 +10219,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10285,7 +10274,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10340,7 +10329,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10397,7 +10386,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10454,7 +10443,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10480,7 +10469,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10505,7 +10494,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10562,7 +10551,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10581,7 +10570,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10604,7 +10593,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10625,7 +10614,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10682,7 +10671,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10739,7 +10728,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10796,18 +10785,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10866,7 +10855,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10926,7 +10915,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -10981,18 +10970,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11049,7 +11038,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11108,7 +11097,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11165,18 +11154,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11234,7 +11223,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11292,7 +11281,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11347,18 +11336,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11416,10 +11405,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11442,14 +11431,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11504,7 +11493,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11559,7 +11548,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11616,7 +11605,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11671,11 +11660,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11685,7 +11674,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11712,7 +11701,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11739,7 +11728,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11794,11 +11783,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11808,7 +11797,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11863,7 +11852,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11918,7 +11907,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -11973,7 +11962,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12028,7 +12017,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12084,7 +12073,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12139,11 +12128,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12153,7 +12142,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12178,7 +12167,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12203,7 +12192,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12228,7 +12217,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12255,10 +12244,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12281,7 +12270,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12302,7 +12291,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12359,7 +12348,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12416,7 +12405,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12473,7 +12462,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12530,7 +12519,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12587,7 +12576,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12646,7 +12635,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12703,7 +12692,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12760,7 +12749,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12817,7 +12806,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12874,7 +12863,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12932,7 +12921,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -12989,7 +12978,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13015,7 +13004,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13039,7 +13028,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13096,18 +13085,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13163,7 +13152,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13219,7 +13208,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13274,7 +13263,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13329,11 +13318,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13354,7 +13343,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13411,7 +13400,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13468,10 +13457,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13494,7 +13483,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13504,7 +13493,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13561,7 +13550,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13618,7 +13607,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13675,7 +13664,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13732,7 +13721,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13789,11 +13778,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13816,7 +13805,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13873,7 +13862,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13930,7 +13919,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -13957,18 +13946,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14020,7 +14009,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14072,11 +14061,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14130,7 +14119,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14185,7 +14174,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14239,7 +14228,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14295,7 +14284,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14352,7 +14341,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14371,7 +14360,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14394,7 +14383,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14415,7 +14404,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14473,7 +14462,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14530,7 +14519,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14580,688 +14569,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15283,16 +15272,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15304,7 +15293,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15317,7 +15306,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15338,24 +15327,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>37878.03183096979</v>
+        <v>40403.233953034447</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15367,7 +15356,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15383,7 +15372,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15399,7 +15388,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15415,13 +15404,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>17414.74683248506</v>
+        <v>19939.948954549716</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15429,7 +15418,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15443,13 +15432,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15457,10 +15446,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15470,13 +15459,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15486,7 +15475,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15496,13 +15485,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.46666798264237</v>
+        <v>36.110746337765448</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15510,10 +15499,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15531,7 +15520,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15545,15 +15534,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2925.9426081188321</v>
+        <v>2939.5516435054315</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15567,15 +15556,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2825.2326388713932</v>
+        <v>2851.5749918698484</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15589,15 +15578,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2727.9890731951241</v>
+        <v>2766.2313578409162</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15611,15 +15600,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2634.0925986345837</v>
+        <v>2683.4419389001473</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15633,15 +15622,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2543.4280094292781</v>
+        <v>2603.1302909777432</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15655,15 +15644,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2455.8840651625846</v>
+        <v>2525.2222578675369</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15677,15 +15666,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2371.3533542759428</v>
+        <v>2449.645902754447</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15699,15 +15688,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2289.7321622808322</v>
+        <v>2376.331441791222</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15721,15 +15710,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2210.9203445068565</v>
+        <v>2305.211179663137</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15743,15 +15732,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2134.8212032297902</v>
+        <v>2236.2194470811478</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15765,15 +15754,15 @@
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2061.3413690288453</v>
+        <v>2169.2925401457869</v>
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15787,15 +15776,15 @@
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1990.3906862275724</v>
+        <v>2104.3686615258189</v>
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15809,15 +15798,15 @@
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1921.8821022778536</v>
+        <v>2041.3878633973254</v>
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15831,15 +15820,15 @@
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1855.7315609512602</v>
+        <v>1980.2919920905549</v>
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15853,15 +15842,15 @@
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0.31524170496588994</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1791.8578992067253</v>
+        <v>1921.0246343934034</v>
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15875,15 +15864,15 @@
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0.29189046756100923</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1730.1827476080032</v>
+        <v>1863.531065461965</v>
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15897,15 +15886,15 @@
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0.27026895144537894</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1670.6304341687189</v>
+        <v>1807.7581982900431</v>
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15919,15 +15908,15 @@
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0.25024902911609154</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1613.1278915070429</v>
+        <v>1753.6545346909659</v>
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15941,15 +15930,15 @@
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0.23171206399638106</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1557.6045671960755</v>
+        <v>1701.1701177464524</v>
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15963,15 +15952,15 @@
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0.21454820740405653</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1503.9923371999307</v>
+        <v>1650.2564856786153</v>
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15985,15 +15974,15 @@
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0.19865574759634863</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1452.2254222893298</v>
+        <v>1600.8666271025033</v>
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16007,15 +15996,15 @@
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0.18394050703365611</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1402.24030733414</v>
+        <v>1552.9549376178861</v>
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16029,15 +16018,15 @@
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0.17031528429042234</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1353.9756633738355</v>
+        <v>1506.477177700172</v>
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16051,15 +16040,15 @@
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0.1576993373059466</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1307.3722723702681</v>
+        <v>1461.3904318515993</v>
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16073,15 +16062,15 @@
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>0.1460179049129135</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1262.3729545504236</v>
+        <v>1417.653068974972</v>
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16095,15 +16084,15 @@
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
-        <v>0.13520176380825324</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1218.922498250015</v>
+        <v>1375.2247039333579</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16117,15 +16106,15 @@
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
-        <v>0.12518681834097523</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1176.9675921718349</v>
+        <v>1334.0661602602434</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16139,15 +16128,15 @@
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
-        <v>0.11591372068608817</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1136.4567599757568</v>
+        <v>1294.1394339857306</v>
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16161,15 +16150,15 @@
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
-        <v>0.10732751915378534</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1097.340297120121</v>
+        <v>1255.407658545357</v>
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16183,21 +16172,21 @@
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
-        <v>9.9377332549801231E-2</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1059.5702098770241</v>
+        <v>1217.8350707391501</v>
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>39500.225209604236</v>
+        <v>42133.573556911186</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16205,30 +16194,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>9.9377332549801231E-2</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3925.4270164468821</v>
+        <v>4812.5401726783011</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>59209.008646836883</v>
+        <v>63557.851989061775</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16238,10 +16227,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>59209.008646836883</v>
+        <v>63557.851989061775</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16265,141 +16254,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37878.031830969783</v>
+        <v>40403.233953034447</v>
       </c>
       <c r="C56" s="124">
-        <v>39100.175419175226</v>
+        <v>41684.440837253023</v>
       </c>
       <c r="D56" s="124">
-        <v>40358.921674525365</v>
+        <v>43002.971778452091</v>
       </c>
       <c r="E56" s="124">
-        <v>41655.876840298384</v>
+        <v>44360.467544731473</v>
       </c>
       <c r="F56" s="124">
-        <v>42992.696893325017</v>
+        <v>45758.619764620693</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>37878.031830969776</v>
+        <v>40403.233953034462</v>
       </c>
       <c r="C57" s="124">
-        <v>40323.444408496289</v>
+        <v>42954.921864000986</v>
       </c>
       <c r="D57" s="124">
-        <v>43013.953538367758</v>
+        <v>45760.733843490714</v>
       </c>
       <c r="E57" s="124">
-        <v>45978.891907147772</v>
+        <v>48851.182137967924</v>
       </c>
       <c r="F57" s="124">
-        <v>49250.871765191005</v>
+        <v>52260.19761025902</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>37878.031830969769</v>
+        <v>40403.233953034454</v>
       </c>
       <c r="C58" s="124">
-        <v>41837.578963488471</v>
+        <v>44563.499625322547</v>
       </c>
       <c r="D58" s="124">
-        <v>46475.124271124892</v>
+        <v>49438.161185751713</v>
       </c>
       <c r="E58" s="124">
-        <v>51925.365918460499</v>
+        <v>55169.858404293242</v>
       </c>
       <c r="F58" s="124">
-        <v>58349.632359122683</v>
+        <v>61929.521631825875</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>37878.031830969761</v>
+        <v>40403.233953034462</v>
       </c>
       <c r="C59" s="124">
-        <v>43380.239256986337</v>
+        <v>46240.468184706413</v>
       </c>
       <c r="D59" s="124">
-        <v>50200.472511363179</v>
+        <v>53488.272898371215</v>
       </c>
       <c r="E59" s="124">
-        <v>58708.676430178501</v>
+        <v>62545.341116876967</v>
       </c>
       <c r="F59" s="124">
-        <v>69381.647865226274</v>
+        <v>73926.032556884777</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>37878.031830969761</v>
+        <v>40403.233953034462</v>
       </c>
       <c r="C60" s="124">
-        <v>44814.998932173861</v>
+        <v>47836.555211654224</v>
       </c>
       <c r="D60" s="124">
-        <v>53870.067261668366</v>
+        <v>57570.929978183252</v>
       </c>
       <c r="E60" s="124">
-        <v>65817.37960059561</v>
+        <v>70455.162786582179</v>
       </c>
       <c r="F60" s="124">
-        <v>81729.404180137062</v>
+        <v>87667.063979068349</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>37878.031830969761</v>
+        <v>40403.233953034462</v>
       </c>
       <c r="C61" s="124">
-        <v>46080.656552495595</v>
+        <v>49277.46450669528</v>
       </c>
       <c r="D61" s="124">
-        <v>57306.675266102364</v>
+        <v>61483.837759397487</v>
       </c>
       <c r="E61" s="124">
-        <v>72925.179393986153</v>
+        <v>78549.08501650118</v>
       </c>
       <c r="F61" s="124">
-        <v>94972.631581173628</v>
+        <v>102749.65347971194</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16409,7 +16398,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16432,193 +16421,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>14.592547258724675</v>
+        <v>16.708520098210514</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>15.616632664007044</v>
+        <v>17.782097118077825</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>16.671388980284682</v>
+        <v>18.886949531760173</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>17.758162146213571</v>
+        <v>20.024452207710574</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>18.878339774280661</v>
+        <v>21.196022632470683</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>14.59254725872467</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>16.641661090116681</v>
+        <v>18.846686491811898</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>18.896151609292211</v>
+        <v>21.197794107882654</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.38059790540035</v>
+        <v>23.787410438318187</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>24.122327151732307</v>
+        <v>26.643967577141247</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>14.592547258724663</v>
+        <v>16.708520098210521</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>17.9104179811773</v>
+        <v>20.194581309187711</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.796411829788674</v>
+        <v>24.279264817658817</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>26.363398049872877</v>
+        <v>29.082094473399085</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.746560523594841</v>
+        <v>34.746299991266923</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>14.592547258724657</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.203077785742103</v>
+        <v>21.599783646585827</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>24.918037471194946</v>
+        <v>27.673023402725818</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>32.047418619623748</v>
+        <v>35.262320983411847</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>40.990749324060324</v>
+        <v>44.798679982641637</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>14.592547258724657</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.405323133692349</v>
+        <v>22.937211953400308</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>27.992944923441566</v>
+        <v>31.094053116875418</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>38.004099354657718</v>
+        <v>41.890292531522313</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>51.337452569176612</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>56.312866915166872</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>14.592547258724657</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>21.465870772746047</v>
+        <v>24.144610325922145</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>30.872623002991254</v>
+        <v>34.37284276944095</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>43.960023112166873</v>
+        <v>48.672529665639814</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>62.434508619809236</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>68.951201666122259</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16635,7 +16624,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16650,14 +16639,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>62.434508619809236</v>
+        <v>68.951201666122259</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16672,7 +16661,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>43.960023112166873</v>
+        <v>48.672529665639814</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16680,7 +16669,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16695,7 +16684,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>30.872623002991254</v>
+        <v>34.37284276944095</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16703,7 +16692,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16718,7 +16707,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>21.465870772746047</v>
+        <v>24.144610325922145</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16726,7 +16715,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16741,21 +16730,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>14.592547258724657</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16763,23 +16752,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16813,16 +16802,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>444</v>
       </c>
@@ -16834,7 +16823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>443</v>
       </c>
@@ -16847,7 +16836,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>441</v>
       </c>
@@ -16868,24 +16857,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>442</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>23868.00128</v>
+        <v>25459.201365333334</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16895,13 +16884,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>445</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -16909,10 +16898,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -16922,13 +16911,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -16938,7 +16927,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -16948,13 +16937,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>31.262980564067469</v>
+        <v>33.559215680839927</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -16962,10 +16951,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -16983,7 +16972,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -16997,15 +16986,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1843.717810561827</v>
+        <v>1852.293242238859</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17019,15 +17008,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>1780.257658101073</v>
+        <v>1796.8567073307447</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17041,15 +17030,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>1718.9817829344215</v>
+        <v>1743.0793100432509</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17063,15 +17052,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>1659.8150029655089</v>
+        <v>1690.9113947179067</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17085,15 +17074,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>1602.6847238406681</v>
+        <v>1640.3047918203513</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17107,15 +17096,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>1547.5208498796862</v>
+        <v>1591.2127734627261</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17129,15 +17118,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>1494.2556980722984</v>
+        <v>1543.5900102572182</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17151,15 +17140,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>1442.8239150348916</v>
+        <v>1497.3925294609207</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17173,15 +17162,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>1393.1623968255328</v>
+        <v>1452.5776743733566</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17195,15 +17184,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>1345.2102115189336</v>
+        <v>1409.1040649491738</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17217,15 +17206,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>1298.9085244463656</v>
+        <v>1366.9315595896539</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17239,15 +17228,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>1254.2005260087838</v>
+        <v>1326.0212180777439</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17261,15 +17250,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1211.031361974608</v>
+        <v>1286.335265622389</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17283,15 +17272,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1169.3480661766225</v>
+        <v>1247.8370579789698</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17305,15 +17294,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.31524170496588994</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1129.0994955254316</v>
+        <v>1210.4910476136363</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17327,15 +17316,15 @@
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0.29189046756100923</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1090.2362672597299</v>
+        <v>1174.2627508802946</v>
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17349,15 +17338,15 @@
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0.27026895144537894</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1052.7106983563942</v>
+        <v>1139.118716179941</v>
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17371,15 +17360,15 @@
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0.25024902911609154</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1016.4767470260618</v>
+        <v>1105.0264930729411</v>
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17393,15 +17382,15 @@
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0.23171206399638106</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>981.48995622241466</v>
+        <v>1071.9546023157377</v>
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17415,15 +17404,15 @@
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0.21454820740405653</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>947.70739909584847</v>
+        <v>1039.8725067943169</v>
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17437,15 +17426,15 @@
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0.19865574759634863</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>915.08762632461253</v>
+        <v>1008.7505833275909</v>
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17459,15 +17448,15 @@
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0.18394050703365611</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>883.59061525879565</v>
+        <v>978.56009531467328</v>
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17481,15 +17470,15 @@
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0.17031528429042234</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>853.17772081475516</v>
+        <v>949.27316620077647</v>
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17503,15 +17492,15 @@
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0.1576993373059466</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>823.81162805974486</v>
+        <v>920.86275373724118</v>
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17525,15 +17514,15 @@
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0.1460179049129135</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>795.45630642856622</v>
+        <v>893.30262501192487</v>
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17547,15 +17536,15 @@
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0.13520176380825324</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>768.07696551606375</v>
+        <v>866.56733222689763</v>
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17569,15 +17558,15 @@
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0.12518681834097523</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>741.64001239123081</v>
+        <v>840.6321892010759</v>
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17591,15 +17580,15 @@
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0.11591372068608817</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>716.11301038054842</v>
+        <v>815.47324857610113</v>
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17613,15 +17602,15 @@
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0.10732751915378534</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>691.4646392699874</v>
+        <v>791.06727970441136</v>
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17635,21 +17624,21 @@
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>9.9377332549801231E-2</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>667.66465687684558</v>
+        <v>767.39174719909715</v>
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>24890.190442584666</v>
+        <v>26549.536472090313</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17657,30 +17646,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>9.9377332549801231E-2</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2473.5207328406204</v>
+        <v>3032.5154040242592</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>37309.243005988872</v>
+        <v>40049.570141304175</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17690,10 +17679,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>37309.243005988872</v>
+        <v>40049.570141304175</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17717,141 +17706,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>23868.001279999997</v>
+        <v>25459.201365333334</v>
       </c>
       <c r="C51" s="124">
-        <v>24638.107943878487</v>
+        <v>26266.525454634917</v>
       </c>
       <c r="D51" s="124">
-        <v>25431.278966279071</v>
+        <v>27097.368470256646</v>
       </c>
       <c r="E51" s="124">
-        <v>26248.526485762472</v>
+        <v>27952.764305809524</v>
       </c>
       <c r="F51" s="124">
-        <v>27090.893979383956</v>
+        <v>28833.778903475759</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>23868.001279999993</v>
+        <v>25459.201365333342</v>
       </c>
       <c r="C52" s="124">
-        <v>25408.923754298376</v>
+        <v>27067.090882848181</v>
       </c>
       <c r="D52" s="124">
-        <v>27104.288382592465</v>
+        <v>28835.111043366258</v>
       </c>
       <c r="E52" s="124">
-        <v>28972.578506455287</v>
+        <v>30782.488461958688</v>
       </c>
       <c r="F52" s="124">
-        <v>31034.34401181234</v>
+        <v>32930.603918941255</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>23868.001279999989</v>
+        <v>25459.201365333342</v>
       </c>
       <c r="C53" s="124">
-        <v>26363.022046889637</v>
+        <v>28080.700466301016</v>
       </c>
       <c r="D53" s="124">
-        <v>29285.268319680996</v>
+        <v>31152.360284400689</v>
       </c>
       <c r="E53" s="124">
-        <v>32719.617157958135</v>
+        <v>34764.062105635967</v>
       </c>
       <c r="F53" s="124">
-        <v>36767.726107046059</v>
+        <v>39023.513897827652</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>23868.001279999989</v>
+        <v>25459.201365333342</v>
       </c>
       <c r="C54" s="124">
-        <v>27335.095200640651</v>
+        <v>29137.40499362463</v>
       </c>
       <c r="D54" s="124">
-        <v>31632.71385125567</v>
+        <v>33704.448311897075</v>
       </c>
       <c r="E54" s="124">
-        <v>36993.969761567991</v>
+        <v>39411.558881871162</v>
       </c>
       <c r="F54" s="124">
-        <v>43719.305888057068</v>
+        <v>46582.849065837319</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>23868.001279999986</v>
+        <v>25459.201365333334</v>
       </c>
       <c r="C55" s="124">
-        <v>28239.177173977743</v>
+        <v>30143.143817969623</v>
       </c>
       <c r="D55" s="124">
-        <v>33945.027558267066</v>
+        <v>36277.044080378422</v>
       </c>
       <c r="E55" s="124">
-        <v>41473.361328896732</v>
+        <v>44395.757495452133</v>
       </c>
       <c r="F55" s="124">
-        <v>51499.970544673502</v>
+        <v>55241.455115823323</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>23868.001279999989</v>
+        <v>25459.201365333334</v>
       </c>
       <c r="C56" s="124">
-        <v>29036.703239658433</v>
+        <v>31051.100837803064</v>
       </c>
       <c r="D56" s="124">
-        <v>36110.529837126858</v>
+        <v>38742.676094927374</v>
       </c>
       <c r="E56" s="124">
-        <v>45952.183653237284</v>
+        <v>49495.96299203168</v>
       </c>
       <c r="F56" s="124">
-        <v>59844.896436541792</v>
+        <v>64745.414221025305</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17861,7 +17850,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17884,193 +17873,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>20.645304694636323</v>
+        <v>22.009824070727483</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>21.309935983277331</v>
+        <v>22.706022303562275</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>21.994741979301981</v>
+        <v>23.422794374686344</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>22.700597055929062</v>
+        <v>24.161033481791197</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>19.999999999999996</v>
+        <v>21.333333333333343</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>21.291203612922192</v>
+        <v>22.680651442338267</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>22.711820788533547</v>
+        <v>24.16214973771466</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>24.277339494474241</v>
+        <v>25.793939007161548</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>26.004979342629181</v>
+        <v>27.593935103845659</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>19.999999999999993</v>
+        <v>21.333333333333343</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>22.090682615289047</v>
+        <v>23.529997452975682</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>24.539355412403427</v>
+        <v>26.103870130511982</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>27.417140441814269</v>
+        <v>29.13026666775507</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>30.809220827263218</v>
+        <v>32.699440091388873</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>19.999999999999993</v>
+        <v>21.333333333333343</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>22.905223508217151</v>
+        <v>24.415454525754601</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>26.506378544366886</v>
+        <v>28.242371798546404</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>30.9987998807146</v>
+        <v>33.024599269563275</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>36.634241279927629</v>
+        <v>39.033724289994105</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>19.999999999999989</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>23.662791737522266</v>
+        <v>25.258205297003926</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>28.443963246064538</v>
+        <v>30.398057763451252</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>34.752270072692681</v>
+        <v>37.201068472082916</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>43.153986746118946</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>46.289133696429332</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>19.999999999999993</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>24.331072299706555</v>
+        <v>26.019020590402</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>30.258528490515364</v>
+        <v>32.464114309723534</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>38.505263272080136</v>
+        <v>41.474744710615063</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>50.14655038307572</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>54.252899906854118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18087,7 +18076,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18102,14 +18091,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>50.14655038307572</v>
+        <v>54.252899906854118</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18124,7 +18113,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>38.505263272080136</v>
+        <v>41.474744710615063</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18132,7 +18121,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18147,7 +18136,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>30.258528490515364</v>
+        <v>32.464114309723534</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18155,7 +18144,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18170,7 +18159,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>24.331072299706555</v>
+        <v>26.019020590402</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18178,7 +18167,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18193,21 +18182,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>19.999999999999993</v>
+        <v>21.333333333333336</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18215,23 +18204,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18261,7 +18250,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18271,7 +18260,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18284,7 +18273,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18296,7 +18285,7 @@
         <v>-27.74</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18316,7 +18305,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18325,7 +18314,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18342,10 +18331,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>34.064859269378168</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>37.734621832566511</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18370,7 +18359,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18392,7 +18381,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18414,7 +18403,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18425,7 +18414,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
@@ -18439,7 +18428,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18458,7 +18447,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18476,7 +18465,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18487,7 +18476,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18496,7 +18485,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18504,7 +18493,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18516,18 +18505,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18542,13 +18531,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>14.592547258724681</v>
+        <v>16.708520098210517</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18557,7 +18546,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18566,7 +18555,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18578,7 +18567,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18589,13 +18578,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>30.872623002991254</v>
+        <v>34.37284276944095</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18604,7 +18593,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18615,7 +18604,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18624,7 +18613,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18636,7 +18625,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18647,13 +18636,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>21.465870772746047</v>
+        <v>24.144610325922145</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18662,7 +18651,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18673,7 +18662,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18682,7 +18671,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18694,7 +18683,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18705,13 +18694,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>43.960023112166873</v>
+        <v>48.672529665639814</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18720,7 +18709,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18732,20 +18721,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>31.792784972723858</v>
+        <v>35.390706382610965</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18754,12 +18743,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18769,12 +18758,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18783,7 +18772,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18795,7 +18784,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18806,13 +18795,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>14.592547258724657</v>
+        <v>16.708520098210528</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18821,7 +18810,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18832,7 +18821,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18841,7 +18830,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18853,7 +18842,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18864,13 +18853,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>62.434508619809236</v>
+        <v>68.951201666122259</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18879,7 +18868,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18890,13 +18879,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>32.464859269378167</v>
+        <v>36.134621832566509</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18910,7 +18899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -18919,7 +18908,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -18927,7 +18916,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -18940,7 +18929,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -18952,13 +18941,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.46666798264237</v>
+        <v>36.110746337765448</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -18968,7 +18957,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -18976,7 +18965,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -18986,7 +18975,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -18998,7 +18987,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19008,7 +18997,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19021,10 +19010,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>-0.52817248309270792</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>-0.47453230347934405</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19033,12 +19022,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19048,7 +19037,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19061,49 +19050,49 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.5422740524781333</v>
+        <v>2.6516149109837741</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.831216934904582</v>
+        <v>14.133079023418324</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>14.373490987382715</v>
+        <v>16.7846939344021</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19114,18 +19103,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.55726002481272963</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.53549551418648556</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19138,24 +19127,24 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10870597389897529</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.14522234161809888</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19164,7 +19153,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19176,23 +19165,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>17.993416479908618</v>
+        <v>20.027356181723611</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>21.274057798092517</v>
+        <v>23.307997499907511</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19203,58 +19192,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.34470506643597709</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.35496772021283307</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>4.1233551795966088</v>
+        <v>4.1608411837951351</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>25.771651988214895</v>
+        <v>29.086945769356873</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>29.895007167811503</v>
+        <v>33.247786953152008</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19264,18 +19253,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>7.9157962159738249E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>7.9891105344645608E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>422</v>
       </c>
@@ -19284,7 +19273,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19294,23 +19283,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>23.269525289089753</v>
+        <v>25.899865746151637</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>27.12969029059159</v>
+        <v>29.760030747653474</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19320,19 +19309,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.16438328980676686</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.17586774670093841</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19340,7 +19329,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19348,7 +19337,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287A7226-FEC4-43EA-A075-C6964AF8AD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528911BA-C924-4D37-AAC4-880C69AAADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,29 +3866,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4306,7 +4306,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>27.74</v>
+        <v>27.88</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>33104.917775359994</v>
+        <v>33271.993784320002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4364,13 +4364,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14522234161809888</v>
+        <v>0.14320511727220997</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4570,22 +4570,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4597,13 +4597,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4623,13 +4623,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4658,13 +4658,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4750,13 +4750,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4772,7 +4772,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4794,22 +4794,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.1534513604289755E-2</v>
+        <v>9.1074871139992741E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.7678442682047588E-2</v>
+        <v>5.7388809182209476E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4937,22 +4937,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4989,13 +4989,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5008,13 +5008,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5190,13 +5190,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5339,13 +5339,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5358,22 +5358,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5706,13 +5706,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5763,22 +5763,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5802,17 +5802,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5829,6 +5818,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.7678442682047588E-2</v>
+        <v>5.7388809182209476E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.7678442682047588E-2</v>
+        <v>5.7388809182209476E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14469,50 +14469,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.1534513604289755E-2</v>
+        <v>9.1074871139992741E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6967416662683197E-2</v>
+        <v>7.6580923178724239E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.1620779005974036E-2</v>
+        <v>7.1261133774236721E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3137070674632438E-2</v>
+        <v>3.2970672184874601E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-6.0111914897464499E-3</v>
+        <v>-5.9810061666272065E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.5524908587114325E-2</v>
+        <v>-2.5396734727638138E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.9633059554981241E-2</v>
+        <v>2.9484256529956229E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.31527037979137534</v>
+        <v>-0.31368724302054346</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.33224670952623725</v>
+        <v>0.33057832576247564</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10925869154981362</v>
+        <v>0.10871004675723923</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.8364365873728224E-2</v>
+        <v>2.822193362041682E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14526,43 +14526,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.294840116001885E-2</v>
+        <v>8.2531874037981456E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5969100401097467E-2</v>
+        <v>8.553740477498005E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1530158028741672E-2</v>
+        <v>7.117096785212676E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0931960228645049E-2</v>
+        <v>3.0776634746865626E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0904724260293812E-2</v>
+        <v>1.0849965960564933E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8390116330049688E-2</v>
+        <v>5.8096909146182867E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.3097425001802015</v>
+        <v>-0.30818712177183605</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.33197484659454013</v>
+        <v>0.33030782799614572</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11001386636008327</v>
+        <v>0.10946142944148887</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9543924089778661E-2</v>
+        <v>1.9445783868380917E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-27.74</v>
+        <v>-27.88</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>27.74</v>
+        <v>27.88</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>27.74</v>
+        <v>27.88</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14522234161809888</v>
+        <v>0.14320511727220997</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292AC9D4-2FD7-4981-B4BC-6EFE00035CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCE6649-057D-4A13-A71B-97B750D24CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>27.88</v>
+        <v>27.204999999999998</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>33271.993784320002</v>
+        <v>32466.448741119999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14320511727220997</v>
+        <v>0.15306218903536783</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4569,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4622,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4657,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4749,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4793,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.1074871139992741E-2</v>
+        <v>9.3334585825509936E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.7388809182209476E-2</v>
+        <v>5.8812718250321638E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4936,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4988,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5007,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5144,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5189,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5338,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5357,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5705,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5762,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5801,6 +5801,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5817,17 +5828,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.7388809182209476E-2</v>
+        <v>5.8812718250321638E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.7388809182209476E-2</v>
+        <v>5.8812718250321638E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14471,50 +14471,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.1074871139992741E-2</v>
+        <v>9.3334585825509936E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6580923178724239E-2</v>
+        <v>7.8481019600177601E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.1261133774236721E-2</v>
+        <v>7.3029237626381902E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2970672184874601E-2</v>
+        <v>3.3788727826293108E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-5.9810061666272065E-3</v>
+        <v>-6.1294045920075911E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.5396734727638138E-2</v>
+        <v>-2.6026868744956858E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.9484256529956229E-2</v>
+        <v>3.0215808566630385E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.31368724302054346</v>
+        <v>-0.32147033028534283</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.33057832576247564</v>
+        <v>0.33878050807784676</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10871004675723923</v>
+        <v>0.11140731863965557</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.822193362041682E-2</v>
+        <v>2.892216538640768E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14528,43 +14528,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2531874037981456E-2</v>
+        <v>8.4579623164084655E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.553740477498005E-2</v>
+        <v>8.7659725974138722E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.117096785212676E-2</v>
+        <v>7.2936834542080276E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0776634746865626E-2</v>
+        <v>3.1540252774953634E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0849965960564933E-2</v>
+        <v>1.1119171144295179E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8096909146182867E-2</v>
+        <v>5.9538387318345092E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30818712177183605</v>
+        <v>-0.31583374214294391</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.33030782799614572</v>
+        <v>0.33850329882494185</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10946142944148887</v>
+        <v>0.11217734434216908</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9445783868380917E-2</v>
+        <v>1.9928265181049808E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-27.88</v>
+        <v>-27.204999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>27.88</v>
+        <v>27.204999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>27.88</v>
+        <v>27.204999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19135,7 +19135,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14320511727220997</v>
+        <v>0.15306218903536783</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4B337E-60C5-44F2-9A16-F54DA3976811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD00A95A-6012-4D06-B2B8-87828F62C0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>27.204999999999998</v>
+        <v>26.63</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>32466.448741119999</v>
+        <v>31780.243704320001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15306218903536783</v>
+        <v>0.16172866766885385</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.3334585825509936E-2</v>
+        <v>9.5349883867179783E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.8812718250321638E-2</v>
+        <v>6.0082613593691332E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13343,12 +13343,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.8812718250321638E-2</v>
+        <v>6.0082613593691332E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.8812718250321638E-2</v>
+        <v>6.0082613593691332E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14542,50 +14542,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3334585825509936E-2</v>
+        <v>9.5349883867179783E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.8481019600177601E-2</v>
+        <v>8.0175596628720674E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.3029237626381902E-2</v>
+        <v>7.4606098746741262E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3788727826293108E-2</v>
+        <v>3.4518300432380918E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-6.1294045920075911E-3</v>
+        <v>-6.2617518560107591E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.6026868744956858E-2</v>
+        <v>-2.6588845820749205E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.0215808566630385E-2</v>
+        <v>3.0868234023852033E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.32147033028534283</v>
+        <v>-0.32841157849841351</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.33878050807784676</v>
+        <v>0.34609552092594142</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11140731863965557</v>
+        <v>0.11381284654869808</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.892216538640768E-2</v>
+        <v>2.9546658255246751E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14599,43 +14599,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4579623164084655E-2</v>
+        <v>8.6405882395002742E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7659725974138722E-2</v>
+        <v>8.9552491367872467E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2936834542080276E-2</v>
+        <v>7.4511700477555162E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1540252774953634E-2</v>
+        <v>3.2221275882186019E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1119171144295179E-2</v>
+        <v>1.1359258392059719E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9538387318345092E-2</v>
+        <v>6.0823951445571844E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31583374214294391</v>
+        <v>-0.32265328407806193</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.33850329882494185</v>
+        <v>0.34581232611838314</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11217734434216908</v>
+        <v>0.1145994987919155</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9928265181049808E-2</v>
+        <v>2.035856005446714E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-27.204999999999998</v>
+        <v>-26.63</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>27.204999999999998</v>
+        <v>26.63</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>27.204999999999998</v>
+        <v>26.63</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15306218903536783</v>
+        <v>0.16172866766885385</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD00A95A-6012-4D06-B2B8-87828F62C0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB03B30-9A0A-4FDC-9CCF-D24C7CBBCB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>5023.2701205832382</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>1164</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-1164</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-912</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-912</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-12.097342754012749</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-1068.9302313516419</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>2548</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>3030.2425464775833</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.15660042549334799</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.17178673682581444</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.29736257886212014</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.29274978196110413</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.7899036999493159</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.7899036999493159</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>19869</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.40281804358844397</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>3.955391512509995</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>1334</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>-594.28499848473007</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>0</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,349 +6030,349 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>25846</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>26640</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>26485</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>26042</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>26185</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>24977</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>26268</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>26232</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>26487</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>18338</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>16878</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>17714</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>18363</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>17360</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>17008</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>16830</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>17347</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>16529</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>16901</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>12577</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>3616</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>3692</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>4488</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>5222</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>7049</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>5077</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>19141</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>2930</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>3444</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>3122</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335"/>
-      <c r="D7" s="335"/>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
-      <c r="G7" s="335"/>
-      <c r="H7" s="335"/>
-      <c r="I7" s="335"/>
-      <c r="J7" s="335"/>
-      <c r="K7" s="335"/>
-      <c r="L7" s="335"/>
-      <c r="M7" s="335"/>
+      <c r="C7" s="322"/>
+      <c r="D7" s="322"/>
+      <c r="E7" s="322"/>
+      <c r="F7" s="322"/>
+      <c r="G7" s="322"/>
+      <c r="H7" s="322"/>
+      <c r="I7" s="322"/>
+      <c r="J7" s="322"/>
+      <c r="K7" s="322"/>
+      <c r="L7" s="322"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>912</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>912</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>921</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>2047</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>1394</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>1361</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>1284</v>
       </c>
-      <c r="J12" s="334">
+      <c r="J12" s="321">
         <v>1234</v>
       </c>
-      <c r="K12" s="334">
+      <c r="K12" s="321">
         <v>1134</v>
       </c>
-      <c r="L12" s="334">
+      <c r="L12" s="321">
         <v>1321</v>
       </c>
-      <c r="M12" s="334"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334"/>
-      <c r="D13" s="334"/>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
-      <c r="I13" s="334"/>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="321"/>
+      <c r="E13" s="321"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>1890</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>787</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>598</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>684</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>669</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>728</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>-1067</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>-5460</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>1381</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>366</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>2746</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>2846</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>2368</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>1024</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>361</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>1933</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>-10254</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>10990</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>3642</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>647</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>2</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>-9</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>5</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>12</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>5</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>-2</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>-62</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>-9</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>10</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>13</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6368,179 +6384,179 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>1164</v>
       </c>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334">
+      <c r="C20" s="321">
         <v>1164</v>
       </c>
-      <c r="D20" s="334">
+      <c r="D20" s="321">
         <v>1164</v>
       </c>
-      <c r="E20" s="334">
+      <c r="E20" s="321">
         <v>1013</v>
       </c>
-      <c r="F20" s="334">
+      <c r="F20" s="321">
         <v>916</v>
       </c>
-      <c r="G20" s="334">
+      <c r="G20" s="321">
         <v>905</v>
       </c>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334">
+      <c r="C21" s="321">
         <v>589</v>
       </c>
-      <c r="D21" s="334">
+      <c r="D21" s="321">
         <v>589</v>
       </c>
-      <c r="E21" s="334">
+      <c r="E21" s="321">
         <v>806</v>
       </c>
-      <c r="F21" s="334">
+      <c r="F21" s="321">
         <v>1483</v>
       </c>
-      <c r="G21" s="334">
+      <c r="G21" s="321">
         <v>-406</v>
       </c>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>4184</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>3976</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>2469</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>5364</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>4929</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>3552</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>2574</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>527</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>5238</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>2467</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-1023</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-916</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-1091</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>4038</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-522</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>1511</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>288</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>1156</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-1113</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-9704</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-3008</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-2678</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-3714</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-9344</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-3331</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-3913</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-3363</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-4226</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-4621</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>10183</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6573,112 +6589,112 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>2147</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>2147</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>2112</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>2120</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>1957</v>
       </c>
-      <c r="H28" s="334"/>
-      <c r="I28" s="334"/>
-      <c r="J28" s="334"/>
-      <c r="K28" s="334"/>
-      <c r="L28" s="334"/>
-      <c r="M28" s="334"/>
+      <c r="H28" s="321"/>
+      <c r="I28" s="321"/>
+      <c r="J28" s="321"/>
+      <c r="K28" s="321"/>
+      <c r="L28" s="321"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>3376</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>3376</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>3614</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>3651</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>2729</v>
       </c>
-      <c r="H29" s="334"/>
-      <c r="I29" s="334"/>
-      <c r="J29" s="334"/>
-      <c r="K29" s="334"/>
-      <c r="L29" s="334"/>
-      <c r="M29" s="334"/>
+      <c r="H29" s="321"/>
+      <c r="I29" s="321"/>
+      <c r="J29" s="321"/>
+      <c r="K29" s="321"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>38962</v>
       </c>
-      <c r="D30" s="336"/>
-      <c r="E30" s="336"/>
-      <c r="F30" s="336"/>
-      <c r="G30" s="336"/>
-      <c r="H30" s="336"/>
-      <c r="I30" s="336"/>
-      <c r="J30" s="336"/>
-      <c r="K30" s="336"/>
-      <c r="L30" s="336"/>
-      <c r="M30" s="336"/>
+      <c r="D30" s="323"/>
+      <c r="E30" s="323"/>
+      <c r="F30" s="323"/>
+      <c r="G30" s="323"/>
+      <c r="H30" s="323"/>
+      <c r="I30" s="323"/>
+      <c r="J30" s="323"/>
+      <c r="K30" s="323"/>
+      <c r="L30" s="323"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>49325</v>
       </c>
-      <c r="D31" s="336"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
-      <c r="G31" s="336"/>
-      <c r="H31" s="336"/>
-      <c r="I31" s="336"/>
-      <c r="J31" s="336"/>
-      <c r="K31" s="336"/>
-      <c r="L31" s="336"/>
-      <c r="M31" s="336"/>
+      <c r="D31" s="323"/>
+      <c r="E31" s="323"/>
+      <c r="F31" s="323"/>
+      <c r="G31" s="323"/>
+      <c r="H31" s="323"/>
+      <c r="I31" s="323"/>
+      <c r="J31" s="323"/>
+      <c r="K31" s="323"/>
+      <c r="L31" s="323"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>134</v>
       </c>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
-      <c r="G32" s="334"/>
-      <c r="H32" s="334"/>
-      <c r="I32" s="334"/>
-      <c r="J32" s="334"/>
-      <c r="K32" s="334"/>
-      <c r="L32" s="334"/>
-      <c r="M32" s="334"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="321"/>
+      <c r="F32" s="321"/>
+      <c r="G32" s="321"/>
+      <c r="H32" s="321"/>
+      <c r="I32" s="321"/>
+      <c r="J32" s="321"/>
+      <c r="K32" s="321"/>
+      <c r="L32" s="321"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6705,47 +6721,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>25846</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>26640</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>26485</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>26042</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>26185</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>24977</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>26268</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>26232</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>26487</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>18338</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6754,47 +6770,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-16878</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-17714</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-18363</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-17360</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-17008</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-16830</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-17347</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-16529</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-16901</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-12577</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6803,47 +6819,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>8968</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>8926</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>8122</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>8682</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>9177</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>8147</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>8921</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>9703</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>9586</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>5761</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6852,47 +6868,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-3616</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-3692</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-4488</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-5222</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-7049</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-5077</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-19141</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-2930</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-3444</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-3122</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6901,47 +6917,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -6950,47 +6966,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-3616</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-3692</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-4488</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-5222</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-7049</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-5077</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-19141</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-2930</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-3444</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-3122</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6999,47 +7015,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7048,47 +7064,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>5352</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>5234</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>3634</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>3460</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>2128</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>3070</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>-10220</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>6773</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>6142</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>2639</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7195,47 +7211,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-1890</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-787</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-598</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-684</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-669</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-728</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>1067</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>5460</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-1381</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-366</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7244,47 +7260,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>2746</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>2846</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>2368</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>1024</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>361</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>1933</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>-10254</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>10990</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>3642</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>647</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7293,47 +7309,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-2</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-5</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-12</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-5</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-10</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-13</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7347,47 +7363,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-912</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-912</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-921</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-2047</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-1394</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-1361</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-1284</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>-1234</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>-1134</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>-1321</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7396,47 +7412,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7652,47 +7668,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-1164</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7701,47 +7717,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-1164</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-1164</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-1013</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-916</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-905</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7750,47 +7766,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>-589</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>-589</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>-806</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>-1483</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>406</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7799,47 +7815,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>153</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>382</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>-2336</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>58</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>1076</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>1150</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>-501</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-2543</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-496</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>2946</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8221,115 +8237,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>2147</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>2147</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>2112</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>2120</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>1957</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>3376</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>3376</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>3614</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>3651</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>2729</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>38962</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8338,47 +8354,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>49325</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9459,11 +9475,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-1866.9533418666667</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-1928.2849984847301</v>
       </c>
@@ -9491,8 +9507,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>1928.2849984847301</v>
       </c>
@@ -9796,54 +9812,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>26253.25</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>25846</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>26640</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>26485</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>26042</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>26185</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>24977</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>26268</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>26232</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>26487</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>18338</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9853,52 +9869,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-17575.979879416762</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-16878</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-17714</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-18363</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-17360</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-17008</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-16830</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-17347</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-16529</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-16901</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-12577</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9908,52 +9924,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>8677.2701205832382</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>8968</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>8926</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>8122</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>8682</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>9177</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>8147</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>8921</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>9703</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>9586</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>5761</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9963,52 +9979,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-3654</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-3616</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-3692</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-4488</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-5222</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-7049</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-5077</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-19141</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-2930</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-3444</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-3122</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10018,54 +10034,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>5023.2701205832382</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>5352</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>5234</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>3634</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>3460</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>2128</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>3070</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>-10220</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>6773</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>6142</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>2639</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10075,52 +10091,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>1164</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>1164</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10130,52 +10146,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-1164</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-1164</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-1164</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-1013</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-916</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-905</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10185,54 +10201,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10242,52 +10258,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-912</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-912</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-912</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-921</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-2047</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-1394</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-1361</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-1284</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>-1234</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>-1134</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>-1321</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10297,52 +10313,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>4111.2701205832382</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>4440</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>3158</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1700</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>497</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>-171</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>1709</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>-11504</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>5539</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>5008</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>1318</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10352,52 +10368,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1068.9302313516419</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-1890</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-787</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-598</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-684</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-669</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-728</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>1067</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>5460</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-1381</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-366</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10407,54 +10423,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-12.097342754012749</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-2</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-5</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-12</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-5</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-10</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-13</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10464,54 +10480,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>3030.2425464775833</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>2548</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>2371</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>1097</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>-199</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>-845</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>981</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>-10437</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>10999</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>3617</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>939</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10521,7 +10537,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10530,24 +10546,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10555,71 +10571,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>3030.2425464775833</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>2548</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>2371</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>1097</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>-199</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>-845</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>981</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>-10437</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>10999</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>3617</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>939</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10692,54 +10708,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-17575.979879416762</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-16878</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-17714</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-18363</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-17360</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-17008</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-16830</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-17347</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-16529</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-16901</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-12577</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10749,54 +10765,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>0</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>0</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>0</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>0</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>0</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>0</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>0</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>0</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>0</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10806,54 +10822,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-17575.979879416762</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-16878</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-17714</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-18363</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-17360</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-17008</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-16830</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-17347</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-16529</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-16901</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-12577</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11059,54 +11075,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:H33)</f>
         <v>-3654</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-3616</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-3692</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-4488</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-5222</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-7049</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-5077</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-19141</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-2930</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-3444</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-3122</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11116,7 +11132,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11125,47 +11141,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11175,54 +11191,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-3654</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-3616</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-3692</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-4488</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-5222</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-7049</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-5077</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-19141</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-2930</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-3444</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-3122</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11516,52 +11532,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-912</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-912</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-912</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-921</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-2047</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-1394</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-1361</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-1284</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>-1234</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>-1134</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>-1321</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11571,52 +11587,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11626,54 +11642,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11683,52 +11699,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-912</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-912</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-912</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-921</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-2047</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-1394</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-1361</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-1284</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>-1234</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>-1134</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>-1321</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11875,52 +11891,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -11930,52 +11946,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -11985,52 +12001,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12040,52 +12056,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12095,53 +12111,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>196</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>-689</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>253</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>295</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>296</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>952</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>183</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-9</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>15</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-305</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12151,52 +12167,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>196</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>-689</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>253</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>295</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>296</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>952</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>183</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-9</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>15</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-305</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13571,54 +13587,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>88287</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>88287</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13628,54 +13644,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>2147</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>2147</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>2112</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>2120</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>1957</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>0</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13685,54 +13701,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>3376</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>3376</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>3614</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>3651</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>2729</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13742,54 +13758,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>38962</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>38962</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>0</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>0</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>0</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>0</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>0</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>0</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>0</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>0</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>0</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13799,54 +13815,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>49325</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>49325</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>0</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>0</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>0</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>0</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>0</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>0</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>0</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>0</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>0</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15344,7 +15360,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15383,7 +15399,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>3030.2425464775833</v>
       </c>
@@ -15415,7 +15431,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>40403.233953034447</v>
       </c>
@@ -15423,17 +15439,17 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>19869</v>
       </c>
@@ -15441,15 +15457,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>-594.28499848473007</v>
       </c>
@@ -15457,15 +15473,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>0</v>
       </c>
@@ -15473,15 +15489,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>19939.948954549716</v>
       </c>
@@ -15548,7 +15564,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15558,7 +15574,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15572,10 +15588,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15593,7 +15609,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15615,7 +15631,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15637,7 +15653,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15657,9 +15673,19 @@
         <f t="shared" si="1"/>
         <v>2766.2313578409162</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15679,9 +15705,19 @@
         <f t="shared" si="1"/>
         <v>2683.4419389001473</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15701,9 +15737,19 @@
         <f t="shared" si="1"/>
         <v>2603.1302909777432</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15725,7 +15771,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15747,7 +15793,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15769,7 +15815,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15791,7 +15837,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15813,7 +15859,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15835,7 +15881,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15857,11 +15903,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>5226.7961642457558</v>
       </c>
@@ -15877,13 +15923,23 @@
         <f t="shared" si="1"/>
         <v>2041.3878633973254</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>5450.6429091597538</v>
       </c>
@@ -15899,13 +15955,23 @@
         <f t="shared" si="1"/>
         <v>1980.2919920905549</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>5684.0762848957738</v>
       </c>
@@ -15921,9 +15987,19 @@
         <f t="shared" si="1"/>
         <v>1921.0246343934034</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -15945,7 +16021,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -15967,7 +16043,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -15989,7 +16065,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16011,7 +16087,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16033,7 +16109,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16055,7 +16131,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16077,7 +16153,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16099,7 +16175,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16121,7 +16197,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16143,7 +16219,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16165,11 +16241,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>9401.6894731367938</v>
       </c>
@@ -16185,13 +16261,23 @@
         <f t="shared" si="1"/>
         <v>1334.0661602602434</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>9804.3333718313897</v>
       </c>
@@ -16207,13 +16293,23 @@
         <f t="shared" si="1"/>
         <v>1294.1394339857306</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>10224.221204142301</v>
       </c>
@@ -16229,13 +16325,23 @@
         <f t="shared" si="1"/>
         <v>1255.407658545357</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>10662.091471876032</v>
       </c>
@@ -16251,9 +16357,19 @@
         <f t="shared" si="1"/>
         <v>1217.8350707391501</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16275,7 +16391,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16286,11 +16402,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16300,7 +16416,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>63557.851989061775</v>
@@ -16327,7 +16443,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16349,7 +16465,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16370,14 +16486,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>40403.233953034454</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>44563.499625322547</v>
       </c>
       <c r="D58" s="123">
@@ -16389,16 +16505,26 @@
       <c r="F58" s="123">
         <v>61929.521631825875</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>40403.233953034462</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>46240.468184706413</v>
       </c>
       <c r="D59" s="123">
@@ -16410,16 +16536,26 @@
       <c r="F59" s="123">
         <v>73926.032556884777</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>40403.233953034462</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>47836.555211654224</v>
       </c>
       <c r="D60" s="123">
@@ -16431,16 +16567,26 @@
       <c r="F60" s="123">
         <v>87667.063979068349</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>40403.233953034462</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>49277.46450669528</v>
       </c>
       <c r="D61" s="123">
@@ -16452,26 +16598,56 @@
       <c r="F61" s="123">
         <v>102749.65347971194</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16843,6 +17019,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16945,7 +17191,7 @@
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>25459.201365333334</v>
       </c>
@@ -16953,8 +17199,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18411,7 +18657,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>5352</v>
       </c>
@@ -18419,11 +18665,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for The Kraft Heinz(KHC). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18436,7 +18682,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>2548</v>
       </c>
@@ -18444,8 +18690,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18458,7 +18704,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>3030.2425464775833</v>
       </c>
@@ -18466,8 +18712,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18477,8 +18723,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18491,8 +18737,8 @@
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18510,8 +18756,8 @@
         <v>-2.5150882534886732E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18528,8 +18774,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15650274695607269</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18546,8 +18792,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.3394590575448202</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18573,21 +18819,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18601,8 +18847,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18616,8 +18862,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18637,8 +18883,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18648,8 +18894,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18663,8 +18909,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18674,8 +18920,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18695,8 +18941,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18706,8 +18952,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18721,8 +18967,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18732,8 +18978,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18753,8 +18999,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18764,8 +19010,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18779,8 +19025,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18791,8 +19037,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18854,8 +19100,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18865,8 +19111,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18880,8 +19126,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18891,8 +19137,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18912,8 +19158,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18923,8 +19169,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18938,8 +19184,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -18949,8 +19195,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB03B30-9A0A-4FDC-9CCF-D24C7CBBCB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5EEC67-F275-40DE-9752-325A86E52194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4335,7 +4335,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>26.63</v>
+        <v>26.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>31780.243704320001</v>
+        <v>31386.421683200002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16172866766885385</v>
+        <v>0.1668198949902282</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.5349883867179783E-2</v>
+        <v>9.6546289254106368E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0082613593691332E-2</v>
+        <v>6.0836501901140684E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13359,12 +13359,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.0082613593691332E-2</v>
+        <v>6.0836501901140684E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.0082613593691332E-2</v>
+        <v>6.0836501901140684E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14558,50 +14558,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.5349883867179783E-2</v>
+        <v>9.6546289254106368E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.0175596628720674E-2</v>
+        <v>8.1181602213795875E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.4606098746741262E-2</v>
+        <v>7.5542220898316331E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.4518300432380918E-2</v>
+        <v>3.4951419791418394E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-6.2617518560107591E-3</v>
+        <v>-6.3403213659911214E-3</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-2.6588845820749205E-2</v>
+        <v>-2.6922470121922101E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.0868234023852033E-2</v>
+        <v>3.1255554070539149E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.32841157849841351</v>
+        <v>-0.33253233214497152</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.34609552092594142</v>
+        <v>0.35043816434440378</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11381284654869808</v>
+        <v>0.11524091648638135</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.9546658255246751E-2</v>
+        <v>2.9917395792289768E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14615,43 +14615,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6405882395002742E-2</v>
+        <v>8.7490062668400106E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9552491367872467E-2</v>
+        <v>9.0676153807089113E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4511700477555162E-2</v>
+        <v>7.5446638164155658E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2221275882186019E-2</v>
+        <v>3.2625573260175421E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1359258392059719E-2</v>
+        <v>1.1501789010667313E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0823951445571844E-2</v>
+        <v>6.1587141710858488E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.32265328407806193</v>
+        <v>-0.32670178536117067</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.34581232611838314</v>
+        <v>0.35015141614192175</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1145994987919155</v>
+        <v>0.1160374392710536</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.035856005446714E-2</v>
+        <v>2.061400966731787E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-26.63</v>
+        <v>-26.3</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>26.63</v>
+        <v>26.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19439,7 +19439,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>26.63</v>
+        <v>26.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16172866766885385</v>
+        <v>0.1668198949902282</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/KHC_Valuation.xlsx
+++ b/financial_models/opportunities/KHC_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3AE32C-E8DC-4035-ADD3-FA01BEA4099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F661A0B9-9795-1846-AE86-1FBDBAC12F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>26.3</v>
+        <v>26.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>31386.421683200002</v>
+        <v>32018.92371712</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1668198949902282</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.15868521802257218</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4523,7 +4534,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,23 +4873,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.6546289254106368E-2</v>
+        <v>9.4639113208460593E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.0836501901140684E-2</v>
+        <v>5.9634737234439066E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4888,7 +4899,7 @@
         <v>0.63012781093037351</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>9.0015205271160664E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>0.17178673682581444</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>0.29274978196110413</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>1.7899036999493159</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>0.40281804358844397</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>3.955391512509995</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,7 +5482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,7 +5517,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5515,7 +5526,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5525,7 +5536,7 @@
         <v>2.6516149109837741</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>14.133079023418324</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.53549551418648556</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>3.2806413181838994</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>20.027356181723611</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.35496772021283307</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>4.1608411837951351</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>29.086945769356873</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>7.9891105344645608E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>3.8601650015018389</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>25.899865746151637</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>0.17586774670093841</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5922,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5941,15 +5952,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>USD</v>
@@ -5998,7 +6009,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +6025,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6058,7 +6069,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6094,7 +6105,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6130,7 +6141,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6146,7 +6157,7 @@
       <c r="L7" s="352"/>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6162,7 +6173,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6178,7 +6189,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6194,7 +6205,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6210,7 +6221,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6246,7 +6257,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6262,7 +6273,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6298,7 +6309,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6334,7 +6345,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6370,13 +6381,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6394,7 +6405,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6420,7 +6431,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6446,7 +6457,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6482,7 +6493,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6518,7 +6529,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6554,7 +6565,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (USD)</v>
@@ -6573,7 +6584,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6581,7 +6592,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6608,7 +6619,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6635,7 +6646,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6654,7 +6665,7 @@
       <c r="L30" s="353"/>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6673,7 +6684,7 @@
       <c r="L31" s="353"/>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6692,7 +6703,7 @@
       <c r="L32" s="351"/>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6708,12 +6719,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6762,7 +6773,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6811,7 +6822,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6860,7 +6871,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6909,7 +6920,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6958,7 +6969,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7007,7 +7018,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7056,7 +7067,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7105,7 +7116,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7154,7 +7165,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7203,7 +7214,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7252,7 +7263,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7301,7 +7312,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7350,12 +7361,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7404,7 +7415,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7453,12 +7464,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7507,7 +7518,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7556,7 +7567,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7605,7 +7616,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7654,13 +7665,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7709,7 +7720,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7758,7 +7769,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7807,7 +7818,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7856,7 +7867,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7905,12 +7916,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7960,7 +7971,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8009,7 +8020,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8059,7 +8070,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8108,7 +8119,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8158,7 +8169,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x1